--- a/v2/output/results.xlsx
+++ b/v2/output/results.xlsx
@@ -36,7 +36,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,6 @@
         <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -92,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -107,9 +101,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -551,7 +542,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -561,7 +552,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -571,7 +562,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -581,7 +572,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -592,7 +583,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
     </row>
@@ -650,20 +641,20 @@
         <v>62</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>77.6%</t>
         </is>
       </c>
     </row>
@@ -677,20 +668,20 @@
         <v>44</v>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -704,20 +695,20 @@
         <v>50</v>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>35.9%</t>
         </is>
       </c>
     </row>
@@ -731,20 +722,20 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>17</v>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -917,13 +908,17 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Line item shows EUR 278,004.50 under immaterielle Vermögensgegenstände</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is immaterielles Anlagevermögen (intangible assets) properly...</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -981,23 +976,27 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Intangible assets shown as single line item</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is selbst geschaffene gewerbliche Schutzrechte (self-created...</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1048,12 +1047,16 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -1061,13 +1064,17 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>No goodwill reported</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is Geschäfts- oder Firmenwert (goodwill) from business combi...</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1131,13 +1138,17 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Prepayments shown under Sachanlagen</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are geleistete Anzahlungen on intangible assets disclosed as...</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1201,13 +1212,17 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>All four categories disclosed</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is Sachanlagen (tangible fixed assets) properly classified i...</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1271,13 +1286,17 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>EUR 260,009</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Grundstücke und grundstücksgleiche Rechte (land and land...</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1341,13 +1360,17 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>EUR 91,533</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is technical equipment and machinery (technische Anlagen und...</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1411,13 +1434,17 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>EUR 1,740,319.50</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are other plant, equipment, and office fixtures (andere Anla...</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,13 +1508,17 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>EUR 219,069.98</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are prepayments and construction in progress (geleistete Anz...</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1546,18 +1577,22 @@
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Financial assets shown; may use §288 exemption</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is Finanzanlagen (financial assets) properly classified into...</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1608,30 +1643,30 @@
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL_DISCLOSURE</t>
-        </is>
-      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Only Beteiligungen shown</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Anteile an verbundenen Unternehmen (shares in affiliated...</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1682,16 +1717,12 @@
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -1699,13 +1730,17 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>No loans to affiliates</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Ausleihungen (loans) to affiliated companies and to comp...</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1756,16 +1791,12 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -1773,13 +1804,17 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>No securities in fixed assets</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Wertpapiere des Anlagevermögens (securities held as non-...</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1830,16 +1865,12 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -1847,13 +1878,17 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>No other loans</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are sonstige Ausleihungen (other loans) disclosed as a final...</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -1917,13 +1952,17 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>EUR 18,756,886.55</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is Vorräte (inventories) properly broken down into raw mater...</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -1974,30 +2013,30 @@
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL_DISCLOSURE</t>
-        </is>
-      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Inventory not broken down</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Roh-, Hilfs- und Betriebsstoffe (raw materials, consumab...</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2055,23 +2094,27 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>No WIP breakdown</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are unfertige Erzeugnisse and unfertige Leistungen (work in ...</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2122,30 +2165,30 @@
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL_DISCLOSURE</t>
-        </is>
-      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>No finished goods breakdown</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are finished goods and merchandise (fertige Erzeugnisse und ...</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2196,30 +2239,30 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL_DISCLOSURE</t>
-        </is>
-      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>No inventory prepayments</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are prepayments on inventory (geleistete Anzahlungen) disclo...</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2283,13 +2326,17 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Breakdown present</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Forderungen und sonstige Vermögensgegenstände (receivabl...</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2340,30 +2387,30 @@
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL_DISCLOSURE</t>
-        </is>
-      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Trade receivables not separate</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Forderungen aus Lieferungen und Leistungen (trade receiv...</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2414,16 +2461,12 @@
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -2431,13 +2474,17 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>No receivables from affiliates</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are receivables from affiliated companies (Forderungen gegen...</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2501,13 +2548,17 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>EUR 15,367.05</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are receivables from companies with participation interests ...</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -2571,13 +2622,17 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>EUR 1,814,848.23</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are sonstige Vermögensgegenstände (other assets) disclosed a...</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -2641,13 +2696,17 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>EUR 0</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Wertpapiere (securities) classified in current assets sp...</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -2711,13 +2770,17 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>EUR 194,604.57</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is liquid cash position (Kassenbestand, Bundesbankguthaben, ...</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -2781,13 +2844,17 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>EUR 61,169.78</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is the Rechnungsabgrenzungsposten (prepaid expenses) on the ...</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -2855,13 +2922,17 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>No deferred tax assets</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are aktive latente Steuern (deferred tax assets) disclosed a...</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -2933,13 +3004,17 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>No asset offsetting</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">Conditional item - trigger condition not applicable: If assets are offset against liabilities per §246 Abs. 2 HGB resulting in a net </t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3003,13 +3078,17 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>All components shown</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is Eigenkapital (equity) properly structured with the five m...</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3073,13 +3152,17 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>EUR 512,000</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is Gezeichnetes Kapital (subscribed capital) disclosed at th...</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3130,30 +3213,30 @@
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Capital reserve not separately shown</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is Kapitalrücklage (capital reserve) disclosed separately an...</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -3217,13 +3300,17 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>EUR 450,000</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Gewinnrücklagen (retained earnings) disclosed with all f...</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -3281,23 +3368,27 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Legal reserve not shown separately</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is the gesetzliche Rücklage (legal reserve) disclosed separa...</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -3369,13 +3460,17 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>No controlling shares</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>Conditional item - trigger condition not applicable: If the company holds shares in a controlling or majority-owned entity</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -3447,13 +3542,17 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>No statutory reserve</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>Conditional item - trigger condition not applicable: If the Articles of Association require additional reserves to be set aside</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -3517,13 +3616,17 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Included in EUR 450,000</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are andere Gewinnrücklagen (other retained earnings) disclos...</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -3587,13 +3690,17 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>EUR 15,967,079.87</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is Gewinnvortrag/Verlustvortrag (profit/loss brought forward...</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -3657,13 +3764,17 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>EUR 301,937.27</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is Jahresüberschuss/Jahresfehlbetrag (annual profit or loss ...</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -3727,13 +3838,17 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Three categories disclosed</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Rückstellungen (provisions) disclosed as three separate ...</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -3797,13 +3912,17 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>TEUR 1,287</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Rückstellungen für Pensionen und ähnliche Verpflichtunge...</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -3867,13 +3986,17 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Heubeck-Richttafeln 2018G, 1.82%</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is the underlying actuarial calculation for pension provisio...</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -3937,13 +4060,17 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>TEUR 44</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Steuerrückstellungen (tax provisions) disclosed as a sep...</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -4007,13 +4134,17 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>TEUR 625</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are sonstige Rückstellungen (other provisions) disclosed as ...</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -4064,12 +4195,16 @@
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -4077,13 +4212,17 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>At settlement amount</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are other provisions measured at the settlement amount that ...</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -4147,13 +4286,17 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Multiple categories</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Verbindlichkeiten (liabilities) disclosed with all eight...</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -4204,14 +4347,14 @@
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -4221,13 +4364,17 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>No bonds</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are Anleihen (bonds) disclosed, with a sub-row showing the c...</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -4291,13 +4438,17 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>EUR 7,253,591.71</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Verbindlichkeiten gegenüber Kreditinstituten (bank loans...</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -4361,13 +4512,17 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>TEUR 30</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are erhaltene Anzahlungen auf Bestellungen (advance payments...</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -4431,13 +4586,17 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>EUR 1,257,000</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Verbindlichkeiten aus Lieferungen und Leistungen (trade ...</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -4488,16 +4647,12 @@
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>ENTITY_SPECIFIC</t>
-        </is>
-      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -4505,13 +4660,17 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>No drafts</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are liabilities from accepted drafts (Wechselverbindlichkeit...</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -4562,16 +4721,12 @@
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -4579,13 +4734,17 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>No payables to affiliates</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Verbindlichkeiten gegenüber verbundenen Unternehmen (pay...</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -4649,13 +4808,17 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>EUR 278,930.99</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are Verbindlichkeiten gegenüber Unternehmen mit Beteiligungs...</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -4719,13 +4882,17 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>EUR 811,000</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Are sonstige Verbindlichkeiten (other liabilities) disclosed...</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -4789,13 +4956,17 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>EUR 3,340</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is the Rechnungsabgrenzungsposten (deferred income) on the l...</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -4863,13 +5034,17 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>No deferred tax liabilities</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are passive latente Steuern (deferred tax liabilities) discl...</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -4920,12 +5095,16 @@
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="n"/>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -4933,13 +5112,17 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Maturity breakdown</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: For liabilities with maturity exceeding one year, is the bre...</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -4990,12 +5173,16 @@
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="n"/>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -5003,13 +5190,17 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Security assignment</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is collateral provided for liabilities disclosed in the Anha...</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -5060,26 +5251,34 @@
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
-      <c r="N60" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Is the nominal capital and changes in capital reserves discl...</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -5130,26 +5329,34 @@
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: For medium GmbH, is the disclosure of the entity's profit ap...</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -5200,12 +5407,16 @@
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="n"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -5213,13 +5424,17 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>TEUR 7,254</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is the total amount of liabilities secured by collateral (Pf...</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -5274,9 +5489,9 @@
           <t>Medium GmbH not providing detailed provision breakdown in Anhang</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5291,13 +5506,17 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Medium GmbH</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Provisions detailed disclosure exemption</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -5475,13 +5694,17 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Gesamtkostenverfahren</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is the profit and loss account (Gewinn- und Verlustrechnung)...</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -5532,30 +5755,30 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Rohergebnis present</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Revenue (Umsatzerlöse) - Line item 1 of Gesamtkostenverfahre...</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -5606,30 +5829,30 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>In Rohergebnis</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Increase or decrease in inventory of finished goods and work...</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -5680,30 +5903,30 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Not shown</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Other own work capitalized (Andere aktivierte Eigenleistunge...</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5754,30 +5977,34 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Not calculable</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Total operating performance (Gesamtleistung) - Calculated fr...</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -5845,13 +6072,17 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Not separated</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Cost of materials (Materialaufwand) - Line item 4...</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5915,13 +6146,17 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>EUR 4,186,545.21</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Personnel costs (Personalaufwand) - Line item 5...</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5985,13 +6220,17 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>EUR 510,704.32</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Depreciation and amortization (Abschreibungen) - Line item 6...</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -6055,13 +6294,17 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>EUR 4,432,041.45</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Other operating expenses (Sonstige betriebliche Aufwendungen...</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6112,30 +6355,34 @@
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Not shown</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Operating result (Betriebsergebnis) - Calculated as gross pr...</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6199,13 +6446,17 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>EUR 8,007</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Income from equity interests (Erträge aus Beteiligungen) - L...</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -6256,16 +6507,12 @@
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -6273,13 +6520,17 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Income from other securities and loans (Erträge aus anderen ...</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -6343,13 +6594,17 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>EUR 179,710.83</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Other interest and similar income (Sonstige Zinsen und ähnli...</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6400,16 +6655,12 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -6417,13 +6668,17 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>No such line</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Depreciation and amortization of financial assets and securi...</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -6487,13 +6742,17 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>EUR 457,906.42</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Interest and similar expenses (Zinsen und ähnliche Aufwendun...</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6557,13 +6816,17 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>EUR 46,156.90</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Tax on income (Steuern vom Einkommen und vom Ertrag) - Line ...</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6627,13 +6890,17 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>EUR 36,824.96</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Other taxes (Sonstige Steuern) - Line item 14...</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6697,13 +6964,17 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>EUR 8,007</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Income from equity holdings (Erträge aus Beteiligungen) - Li...</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -6754,16 +7025,12 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>ENTITY_SPECIFIC</t>
-        </is>
-      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -6771,13 +7038,17 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>No pooling</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Income from profit pooling, profit transfer or partial profi...</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6828,16 +7099,12 @@
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>ENTITY_SPECIFIC</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -6845,13 +7112,17 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>No pooling</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Expenses from loss absorption (Verluste aus Gewinnabführung)...</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -6915,13 +7186,17 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>EUR 301,937.27</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Annual profit (Jahresüberschuss) - Line item 17...</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -6972,14 +7247,14 @@
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6989,13 +7264,17 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Profit not loss</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Net loss (Jahresfehlbetrag) - Line item 18...</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -7059,13 +7338,17 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>EUR 16,505,583.97</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Profit/loss brought forward (Gewinnvortrag/Verlustvortrag) -...</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -7116,26 +7399,30 @@
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Appropriation to other revenue reserves (Entnahme aus der Ka...</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -7186,26 +7473,30 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Appropriation to other revenue reserves (Einstellung in Gewi...</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -7269,13 +7560,17 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>EUR 15,967,079.87</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Undistributed profit (Bilanzgewinn) - Line item 21...</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -7326,14 +7621,14 @@
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -7343,13 +7638,17 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Profit</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Uncovered loss (Bilanzverlust) - Line item 21 alternative...</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -7400,26 +7699,30 @@
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Does the entity have a chart of accounts (Kontenplan) that m...</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7470,12 +7773,16 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -7483,13 +7790,17 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Prior year shown</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are comparative figures for the prior financial year disclos...</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7544,12 +7855,16 @@
           <t>If material changes in business activities require reclassification of prior year figures</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -7557,13 +7872,17 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>No reclassifications</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>Conditional item - trigger condition not applicable: If material changes in business activities require reclassification of prior yea</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -7610,30 +7929,42 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Material cost breakdown exemption</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -7680,30 +8011,42 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Merchandise cost breakdown exemption</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -7750,30 +8093,42 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Services cost breakdown exemption</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -7820,16 +8175,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="n"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EXEMPTION_CLAIMED</t>
+        </is>
+      </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -7837,13 +8200,17 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>EUR 3,562,103.98</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Wages/salaries breakdown exemption</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -7890,16 +8257,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="n"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EXEMPTION_CLAIMED</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -7907,13 +8282,17 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>EUR 624,441.23</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Social security/pension breakdown exemption</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -7960,16 +8339,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="n"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EXEMPTION_CLAIMED</t>
+        </is>
+      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -7977,13 +8364,17 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>63 employees</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Employee count breakdown exemption</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -8038,26 +8429,34 @@
           <t>If disclosure is not prohibited by §286 Abs. 2 and would not cause significant harm to the company</t>
         </is>
       </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Revenue by activity exemption</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -8112,26 +8511,34 @@
           <t>If disclosure is not prohibited by §286 Abs. 2 and would not cause significant harm to the company</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Revenue by geography exemption</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -8186,30 +8593,34 @@
           <t>If disclosure per §285 Nr. 14 would seriously harm the company</t>
         </is>
       </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>No explicit §286</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Protective clause invocation</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -8264,12 +8675,16 @@
           <t>If two of three thresholds exceeded: €12M revenue, €6M assets, 50 employees</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="n"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>EXEMPTION_CLAIMED</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -8277,13 +8692,17 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Medium GmbH</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - §288 Abs. 2 eligibility</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -8338,9 +8757,9 @@
           <t>If §288 Abs. 2 applies (medium-sized GmbH)</t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -8355,13 +8774,17 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>§288 applied</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - §288 Abs. 2 exemptions applied</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -8425,13 +8848,17 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Lagebericht present</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Is the entity required to provide a management report (Lageb...</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -8482,12 +8909,16 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="n"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -8495,13 +8926,17 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Vertical format</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is there a clear presentation of the GuV using the verticall...</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -8552,12 +8987,16 @@
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="n"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -8565,13 +9004,17 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>No netting</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are material items in the GuV not netted but shown separatel...</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -8749,13 +9192,17 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Section II</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Have the accounting and valuation methods used been disclose...</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -8819,13 +9266,17 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Warenbestand changed</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Have any changes to accounting and valuation methods been di...</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -8876,12 +9327,16 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="n"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -8889,13 +9344,17 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>No estimate changes</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has the impact of any material changes in estimates been dis...</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -8946,26 +9405,30 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Has the name and registered office of subsidiaries been disc...</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9016,26 +9479,30 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Has the equity ( Eigenkapital) of subsidiaries been disclose...</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9086,26 +9553,34 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has an exemption from preparing consolidated accounts (Konze...</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -9157,29 +9632,37 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Entity invokes §288 Abs. 2 exemption</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Revenue segmentation exemption</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9230,26 +9713,34 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has a disclosure of stock movements / changes in inventories...</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -9300,26 +9791,30 @@
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Have other operating income (sonstige Erträge) been broken d...</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -9370,16 +9865,12 @@
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -9387,13 +9878,17 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>R&amp;D not disclosed</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Has research and development (Forschung und Entwicklung) exp...</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9445,29 +9940,37 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Entity invokes §288 Abs. 2 exemption</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Material cost breakdown exemption</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -9519,29 +10022,37 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Entity invokes §288 Abs. 2 exemption</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Personnel cost breakdown exemption</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -9592,12 +10103,16 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -9605,13 +10120,17 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Linear depreciation</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have depreciation and amortization methods and periods been ...</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -9675,13 +10194,17 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Shareholder loan</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Has information on related party transactions (Nahestehende ...</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -9732,12 +10255,16 @@
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="n"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -9745,13 +10272,17 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>EUR 2,076,950 + 238,636</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have off-balance sheet commitments (außerbilanzielle Verpfli...</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -9802,12 +10333,16 @@
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -9815,13 +10350,17 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>No restatements</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have any restatements of prior year figures (Rückwirkung von...</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -9872,12 +10411,16 @@
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -9885,13 +10428,17 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>No events</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have subsequent events (nachträgliche Ereignisse) after the ...</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9942,12 +10489,16 @@
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -9955,13 +10506,17 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63 employees</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have audit fees (Honorar des Abschlussprüfers) for the audit...</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -10012,12 +10567,16 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -10025,13 +10584,17 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63 employees</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have audit fees (Honorar des Abschlussprüfers) for the audit...</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10082,14 +10645,14 @@
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>EXEMPTION_CLAIMED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -10099,13 +10662,17 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>§286 Abs. 4</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has management remuneration (Vorstands-/Geschäftsführungsver...</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -10157,7 +10724,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Entity invokes §288 Abs. 2 exemption</t>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -10167,7 +10734,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -10177,13 +10744,17 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>No controlling</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Transactions with controlling entity exemption</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -10234,14 +10805,14 @@
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -10251,13 +10822,17 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>No equity comp</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has any share-based payment (aktienbasierte Vergütung) been ...</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -10308,16 +10883,12 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -10325,13 +10896,17 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>No uncalled capital</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Has any significant uncalled capital (ausstehende Einlagen) ...</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -10382,14 +10957,14 @@
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -10399,13 +10974,17 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>No parent</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has parent company information (Mutterunternehmen) been disc...</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -10457,7 +11036,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Entity invokes §288 Abs. 2 exemption</t>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -10467,7 +11046,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -10477,13 +11056,17 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>No IFRS</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - IFRS transition disclosure exemption</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -10534,14 +11117,14 @@
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -10551,13 +11134,17 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>No consolidation</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has information on consolidated entities (Konsolidierungskre...</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -10608,12 +11195,16 @@
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="n"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -10621,13 +11212,17 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Two stores</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has information on branch offices (Zweigniederlassungen) bee...</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10691,13 +11286,17 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Pension disclosed</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Has information on pension commitments ( Pensionsverpflichtu...</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10765,13 +11364,17 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>No fee breakdown</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have audit fees been broken down by activity (Abschlussprüfe...</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -10822,26 +11425,34 @@
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has a statement on the application of the simplification rul...</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -10892,16 +11503,12 @@
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -10909,13 +11516,17 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>No small company</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Has a statement on the use of the exemption under §264 Abs. ...</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -10966,14 +11577,14 @@
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -10983,13 +11594,17 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>No hedges</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has the disclosure of financial instruments at fair value (B...</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -11036,18 +11651,22 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -11057,13 +11676,17 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>No revenue split</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Revenue disaggregation exemption</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -11131,13 +11754,17 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>No fair value</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has information on the fair value of financial instruments (...</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -11188,12 +11815,16 @@
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="n"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -11201,13 +11832,17 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>EUR 238,636</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has a statement on the recognition and measurement of lease ...</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -11254,18 +11889,22 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
+          <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -11275,13 +11914,17 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>No grants</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - Government grants exemption</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -11332,16 +11975,12 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -11349,13 +11988,17 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>No currency</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Has a statement on the underlying currency for significant t...</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -11410,26 +12053,34 @@
           <t>Entity claims §286 exemption for specific disclosures</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>ENTITY_SPECIFIC</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Conditional item - trigger condition not applicable: Entity claims §286 exemption for specific disclosures</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -11493,13 +12144,17 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Basic disclosures</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Have other mandatory disclosures under §287 HGB been provide...</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -11550,12 +12205,16 @@
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="n"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -11563,13 +12222,17 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>Going concern</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has a statement on the assumption of going concern (Fortführ...</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -11620,12 +12283,16 @@
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="n"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -11633,13 +12300,17 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>31.12.2023</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has the balance sheet date (Bilanzstichtag) been disclosed? ...</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -11690,12 +12361,16 @@
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -11703,13 +12378,17 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>GmbH</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has the legal form (Rechtsform) of the entity been disclosed...</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -11760,12 +12439,16 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="n"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -11773,13 +12456,17 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>Schwäbisch Gmünd</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has the company's registered office (Sitz der Gesellschaft) ...</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -11843,13 +12530,17 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>HiFi audio</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Has the company's object (Unternehmensgegenstand) been discl...</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -11913,13 +12604,17 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Three managers</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>Item disclosed in financial statements: Has a list of managing directors (Geschäftsführer) with name...</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -11970,30 +12665,34 @@
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Owner loan visible but full structure not</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has membership of the Gesellschafterversammlung been disclos...</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -12044,14 +12743,14 @@
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>ENTITY_SPECIFIC</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -12061,13 +12760,17 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>No Aufsichtsrat required</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have the members of the supervisory board (Aufsichtsrat) bee...</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -12122,9 +12825,9 @@
           <t>Entity claims §288 Abs. 2 exemption</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -12139,13 +12842,17 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>§288 Abs. 2</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr"/>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB - §288 Abs. 2 exemption claim disclosure</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Medium GmbH qualifies for §288 Abs. 2 exemptions from certain disclosure requirements</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -12200,12 +12907,16 @@
           <t>Entity claims §288 Abs. 2 exemption</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="n"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>High</t>
@@ -12213,13 +12924,17 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Medium company</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr"/>
+          <t>Conditional item - trigger condition not applicable: Entity claims §288 Abs. 2 exemption</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -12274,14 +12989,14 @@
           <t>Entity invokes 5-year exemption under §288 Abs. 1</t>
         </is>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
+          <t>ENTITY_SPECIFIC</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -12291,13 +13006,17 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>No 5-year exemption</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr"/>
+          <t>Conditional item - trigger condition not applicable: Entity invokes 5-year exemption under §288 Abs. 1</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -12462,26 +13181,34 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Does the Lagebericht present the business progress (Geschäft...</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -12532,26 +13259,34 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Does the Lagebericht present the Lage (position) of the capi...</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -12602,26 +13337,30 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Does the Lagebericht contain a balanced and comprehensive an...</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -12672,26 +13411,34 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Does the Lagebericht include the most significant financial ...</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -12742,26 +13489,34 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Are the financial performance indicators explained with refe...</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -12812,26 +13567,30 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Does the Lagebericht assess and explain the expected future ...</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -12882,26 +13641,30 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Are the underlying assumptions (Annahmen) for the expected d...</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -12952,26 +13715,30 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Does the Lagebericht disclose the risk management objectives...</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -13026,26 +13793,34 @@
           <t>If the company uses hedge accounting (Bilanzierung von Sicherungsgeschäften)</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>ENTITY_SPECIFIC</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Conditional item - trigger condition not applicable: If the company uses hedge accounting (Bilanzierung von Sicherungsgeschäften)</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -13100,26 +13875,34 @@
           <t>If price change risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>ENTITY_SPECIFIC</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Conditional item - trigger condition not applicable: If price change risks are material for assessing the company's position or expec</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -13174,26 +13957,34 @@
           <t>If default risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>ENTITY_SPECIFIC</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Conditional item - trigger condition not applicable: If default risks are material for assessing the company's position or expected d</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -13248,26 +14039,34 @@
           <t>If liquidity risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>ENTITY_SPECIFIC</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Conditional item - trigger condition not applicable: If liquidity risks are material for assessing the company's position or expected</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -13322,26 +14121,34 @@
           <t>If cash flow fluctuation risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>ENTITY_SPECIFIC</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Conditional item - trigger condition not applicable: If cash flow fluctuation risks are material for assessing the company's position</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -13392,26 +14199,30 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Item disclosed in financial statements: Does the Lagebericht include disclosure on the research and ...</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Verified - present in FS structure</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -13462,26 +14273,34 @@
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Does the Lagebericht disclose existing branch offices (beste...</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -13536,26 +14355,34 @@
           <t>If the company is a capital market oriented company (§ 264d HGB - Kapitalmarktorientierte Kapitalgesellschaft)</t>
         </is>
       </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>ENTITY_SPECIFIC</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Conditional item - trigger condition not applicable: If the company is a capital market oriented company (§ 264d HGB - Kapitalmarktor</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -13610,26 +14437,34 @@
           <t>If the company is a capital market oriented company (§ 264d HGB - Kapitalmarktorientierte Kapitalgesellschaft)</t>
         </is>
       </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>ENTITY_SPECIFIC</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Conditional item - trigger condition not applicable: If the company is a capital market oriented company (§ 264d HGB - Kapitalmarktor</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable for this entity</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>verification-agent</t>
+          <t>verification-agent-v2</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -13649,7 +14484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13721,20 +14556,24 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Intangible assets shown as single line item</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is selbst geschaffene gewerbliche Schutzrechte (self-created...</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10011</t>
+          <t>HGB-BIL-10003</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -13744,7 +14583,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Are Anteile an verbundenen Unternehmen (shares in affiliated companies) disclosed separately from Beteiligungen (participations)?</t>
+          <t>Is Geschäfts- oder Firmenwert (goodwill) from business combinations separately recognised and amortised over useful life?</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -13754,20 +14593,24 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Only Beteiligungen shown</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is Geschäfts- oder Firmenwert (goodwill) from business combi...</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10012</t>
+          <t>HGB-BIL-10022</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -13777,7 +14620,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Are Ausleihungen (loans) to affiliated companies and to companies with participation interests disclosed separately from equity items?</t>
+          <t>Are unfertige Erzeugnisse and unfertige Leistungen (work in progress and services not yet billed) disclosed together?</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -13792,15 +14635,19 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>No loans to affiliates</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are unfertige Erzeugnisse and unfertige Leistungen (work in ...</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10013</t>
+          <t>HGB-BIL-10033</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -13810,7 +14657,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Are Wertpapiere des Anlagevermögens (securities held as non-current assets) disclosed separately from current portfolio?</t>
+          <t>Are aktive latente Steuern (deferred tax assets) disclosed as a separate posten under asset side?</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -13825,15 +14672,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>No securities in fixed assets</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are aktive latente Steuern (deferred tax assets) disclosed a...</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10014</t>
+          <t>HGB-BIL-20005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -13843,7 +14694,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Are sonstige Ausleihungen (other loans) disclosed as a final line item under financial assets?</t>
+          <t>Is the gesetzliche Rücklage (legal reserve) disclosed separately and is the required 10% of subscribed capital maintained?</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -13858,15 +14709,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>No other loans</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is the gesetzliche Rücklage (legal reserve) disclosed separa...</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10021</t>
+          <t>HGB-BIL-20016</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -13876,7 +14731,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Are Roh-, Hilfs- und Betriebsstoffe (raw materials, consumables, and supplies) disclosed separately?</t>
+          <t>Are other provisions measured at the settlement amount that reflects the best estimate, with discounting for long-term provisions per §253 Abs. 2?</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -13886,20 +14741,24 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Inventory not broken down</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are other provisions measured at the settlement amount that ...</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10022</t>
+          <t>HGB-BIL-20021</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -13909,7 +14768,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Are unfertige Erzeugnisse and unfertige Leistungen (work in progress and services not yet billed) disclosed together?</t>
+          <t>Are Anleihen (bonds) disclosed, with a sub-row showing the convertible portion if applicable?</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -13919,20 +14778,24 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>No WIP breakdown</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are Anleihen (bonds) disclosed, with a sub-row showing the c...</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10023</t>
+          <t>HGB-BIL-20030</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -13942,7 +14805,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Are finished goods and merchandise (fertige Erzeugnisse und Waren) disclosed as a single line item?</t>
+          <t>Are passive latente Steuern (deferred tax liabilities) disclosed as the final liability item?</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -13952,20 +14815,24 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>No finished goods breakdown</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are passive latente Steuern (deferred tax liabilities) discl...</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10024</t>
+          <t>HGB-BIL-20031</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -13975,7 +14842,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Are prepayments on inventory (geleistete Anzahlungen) disclosed as the final inventory line?</t>
+          <t>For liabilities with maturity exceeding one year, is the breakdown by remaining maturity disclosed in the Anhang per §285 No. 1 HGB?</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -13985,20 +14852,24 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>No inventory prepayments</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: For liabilities with maturity exceeding one year, is the bre...</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10026</t>
+          <t>HGB-BIL-20032</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -14008,7 +14879,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Are Forderungen aus Lieferungen und Leistungen (trade receivables) disclosed separately?</t>
+          <t>Is collateral provided for liabilities disclosed in the Anhang per §285 No. 2 HGB?</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -14018,20 +14889,24 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Trade receivables not separate</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is collateral provided for liabilities disclosed in the Anha...</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10027</t>
+          <t>HGB-BIL-20033</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -14041,7 +14916,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Are receivables from affiliated companies (Forderungen gegen verbundene Unternehmen) disclosed separately?</t>
+          <t>Is the nominal capital and changes in capital reserves disclosed per §285 No. 3 HGB?</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -14056,15 +14931,19 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>No receivables from affiliates</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is the nominal capital and changes in capital reserves discl...</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10033</t>
+          <t>HGB-BIL-20034</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -14074,7 +14953,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Are aktive latente Steuern (deferred tax assets) disclosed as a separate posten under asset side?</t>
+          <t>For medium GmbH, is the disclosure of the entity's profit appropriation proposal required or is the proposal disclosed in the Anhang?</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -14089,15 +14968,19 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>No deferred tax assets</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: For medium GmbH, is the disclosure of the entity's profit ap...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20003</t>
+          <t>HGB-BIL-20035</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -14107,7 +14990,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Is Kapitalrücklage (capital reserve) disclosed separately and showing share premium from capital contributions?</t>
+          <t>Is the total amount of liabilities secured by collateral (Pfandbriefe, etc.) disclosed per §285 No. 3a?</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -14122,25 +15005,29 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Capital reserve not separately shown</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is the total amount of liabilities secured by collateral (Pf...</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20005</t>
+          <t>HGB-GUV-30005</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Is the gesetzliche Rücklage (legal reserve) disclosed separately and is the required 10% of subscribed capital maintained?</t>
+          <t>Total operating performance (Gesamtleistung) - Calculated from lines 1-3</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -14150,30 +15037,34 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL_DISCLOSURE</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Legal reserve not shown separately</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Total operating performance (Gesamtleistung) - Calculated fr...</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20026</t>
+          <t>HGB-GUV-30006</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Are Verbindlichkeiten gegenüber verbundenen Unternehmen (payables to affiliated companies) disclosed separately?</t>
+          <t>Cost of materials (Materialaufwand) - Line item 4</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -14188,25 +15079,29 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>No payables to affiliates</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Cost of materials (Materialaufwand) - Line item 4...</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20030</t>
+          <t>HGB-GUV-30010</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Are passive latente Steuern (deferred tax liabilities) disclosed as the final liability item?</t>
+          <t>Operating result (Betriebsergebnis) - Calculated as gross profit less lines 4-7</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -14221,73 +15116,93 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>No deferred tax liabilities</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Operating result (Betriebsergebnis) - Calculated as gross pr...</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20033</t>
+          <t>HGB-GUV-30022</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Is the nominal capital and changes in capital reserves disclosed per §285 No. 3 HGB?</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Net loss (Jahresfehlbetrag) - Line item 18</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Net loss (Jahresfehlbetrag) - Line item 18...</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20034</t>
+          <t>HGB-GUV-30027</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>For medium GmbH, is the disclosure of the entity's profit appropriation proposal required or is the proposal disclosed in the Anhang?</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Uncovered loss (Bilanzverlust) - Line item 21 alternative</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Uncovered loss (Bilanzverlust) - Line item 21 alternative...</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30002</t>
+          <t>HGB-GUV-30031</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -14297,30 +15212,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Revenue (Umsatzerlöse) - Line item 1 of Gesamtkostenverfahren</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Are comparative figures for the prior financial year disclosed in the GuV per §275 Abs. 3 HGB?</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Rohergebnis present</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are comparative figures for the prior financial year disclos...</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30003</t>
+          <t>HGB-GUV-30090</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -14330,30 +15249,34 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Increase or decrease in inventory of finished goods and work in progress (Bestand an fertigen und unfertigen Erzeugnissen) - Line item 2</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Is there a clear presentation of the GuV using the vertically aligned format per §275 Abs. 1 HGB?</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>In Rohergebnis</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Is there a clear presentation of the GuV using the verticall...</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30004</t>
+          <t>HGB-GUV-30091</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -14363,73 +15286,81 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Other own work capitalized (Andere aktivierte Eigenleistungen) - Line item 3</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Are material items in the GuV not netted but shown separately per §265 Abs. 7 HGB?</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Not shown</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are material items in the GuV not netted but shown separatel...</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30005</t>
+          <t>HGB-ANH-40003</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Total operating performance (Gesamtleistung) - Calculated from lines 1-3</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has the impact of any material changes in estimates been disclosed? (Wesentliche Schätzungsänderungen)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Not calculable</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has the impact of any material changes in estimates been dis...</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30006</t>
+          <t>HGB-ANH-40103</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Cost of materials (Materialaufwand) - Line item 4</t>
+          <t>Has an exemption from preparing consolidated accounts (Konzernabschluss) been disclosed with reasons and criteria? (Befreiung von Konzernabschluss)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -14444,58 +15375,66 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Not separated</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has an exemption from preparing consolidated accounts (Konze...</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30010</t>
+          <t>HGB-ANH-40105</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Operating result (Betriebsergebnis) - Calculated as gross profit less lines 4-7</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has a disclosure of stock movements / changes in inventories been made? (Vorratsbestandsveränderung)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Not shown</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has a disclosure of stock movements / changes in inventories...</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30012</t>
+          <t>HGB-ANH-40110</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Income from other securities and loans (Erträge aus anderen Wertpapieren und Ausleihungen des Finanzanlagevermögens) - Line item 9</t>
+          <t>Have depreciation and amortization methods and periods been disclosed? (Abschreibungsmethoden)</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -14510,25 +15449,29 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have depreciation and amortization methods and periods been ...</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30014</t>
+          <t>HGB-ANH-40112</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Depreciation and amortization of financial assets and securities (Abschreibungen auf Finanzanlagen und auf Wertpapiere des Umlaufvermögens) - Line item 11</t>
+          <t>Have off-balance sheet commitments (außerbilanzielle Verpflichtungen) been disclosed? (Haftungsverhältnisse)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -14543,280 +15486,352 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>No such line</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have off-balance sheet commitments (außerbilanzielle Verpfli...</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30024</t>
+          <t>HGB-ANH-40113</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Appropriation to other revenue reserves (Entnahme aus der Kapitalrücklage, Entnahme aus Gewinnrücklagen) - Line item 20</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Have any restatements of prior year figures (Rückwirkung von Bilanzänderungen) been disclosed? (Rückwirkende Änderungen)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Have any restatements of prior year figures (Rückwirkung von...</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30025</t>
+          <t>HGB-ANH-40114</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Appropriation to other revenue reserves (Einstellung in Gewinnrücklagen) - Line item 20 alternative</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Have subsequent events (nachträgliche Ereignisse) after the balance sheet date been disclosed? (Nachtragsbericht)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Have subsequent events (nachträgliche Ereignisse) after the ...</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30030</t>
+          <t>HGB-ANH-40115</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Does the entity have a chart of accounts (Kontenplan) that maps to the Gesamtkostenverfahren line items per §275 Abs. 2 HGB?</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has the average number of employees (Durchschnittszahl der Beschäftigten) been disclosed? (Beschäftigtenzahl)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Have audit fees (Honorar des Abschlussprüfers) for the audit...</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30040</t>
+          <t>HGB-ANH-40115</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Is the cost of raw materials and supplies (Aufwendungen für Roh-, Hilfs- und Betriebsstoffe) broken down per §285 Nr. 8 HGB?</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Have audit fees (Honorar des Abschlussprüfers) for the auditor been disclosed? (Abschlussprüferhonorar)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Have audit fees (Honorar des Abschlussprüfers) for the audit...</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30041</t>
+          <t>HGB-ANH-40116</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Are the cost of merchandise purchased (Aufwendungen für bezogene Waren) broken down per §285 Nr. 8 HGB?</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has management remuneration (Vorstands-/Geschäftsführungsvergütung) been disclosed individually or in aggregate? (Gesamtbezüge der Organmitglieder)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has management remuneration (Vorstands-/Geschäftsführungsver...</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30042</t>
+          <t>HGB-ANH-40118</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Is the cost of services purchased (Aufwendungen für bezogene Leistungen) broken down per §285 Nr. 8 HGB?</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has any share-based payment (aktienbasierte Vergütung) been disclosed? (Aktienbasierte Vergütung)</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has any share-based payment (aktienbasierte Vergütung) been ...</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30060</t>
+          <t>HGB-ANH-40120</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Is revenue broken down by business activity (Tätigkeit) per §285 Nr. 14 HGB?</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has parent company information (Mutterunternehmen) been disclosed? (Mutterunternehmen)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has parent company information (Mutterunternehmen) been disc...</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30061</t>
+          <t>HGB-ANH-40122</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Is revenue broken down by geographic market ( Märkte) per §285 Nr. 14 HGB?</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has information on consolidated entities (Konsolidierungskreis) been disclosed? (Tochterunternehmen im Konzernabschluss)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has information on consolidated entities (Konsolidierungskre...</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30070</t>
+          <t>HGB-ANH-40123</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>If revenue breakdown by activity or geography is not disclosed, has the entity invoked the protective clause under §286 Abs. 2 HGB?</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has information on branch offices (Zweigniederlassungen) been disclosed? (Zweigniederlassungen)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>No explicit §286</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has information on branch offices (Zweigniederlassungen) bee...</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40101</t>
+          <t>HGB-ANH-40125</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -14826,26 +15841,34 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Has the name and registered office of subsidiaries been disclosed? (Name und Sitz von Tochterunternehmen)</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Have audit fees been broken down by activity (Abschlussprüferleistungen)? (Aufschlüsselung des Prüfungshonorars)</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Have audit fees been broken down by activity (Abschlussprüfe...</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40102</t>
+          <t>HGB-ANH-40126</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -14855,26 +15878,34 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Has the equity ( Eigenkapital) of subsidiaries been disclosed? (Eigenkapital der Tochterunternehmen)</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has a statement on the application of the simplification rule for deferred taxes (§274a HGB) been disclosed? ( Vereinfachungsregelung latente Steuern)</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has a statement on the application of the simplification rul...</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40103</t>
+          <t>HGB-ANH-40128</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -14884,26 +15915,34 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Has an exemption from preparing consolidated accounts (Konzernabschluss) been disclosed with reasons and criteria? (Befreiung von Konzernabschluss)</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has the disclosure of financial instruments at fair value (Bewertungseinheiten) been made? (Bewertungseinheiten)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has the disclosure of financial instruments at fair value (B...</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40104</t>
+          <t>HGB-ANH-40130</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -14913,26 +15952,34 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Has a breakdown of revenue by category and geographic market been disclosed? (Umsatzaufteilung nach Segmenten bzw. Märkten)</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has information on the fair value of financial instruments (Beizulegender Zeitwert) been disclosed? (Fair-Value-Angaben)</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has information on the fair value of financial instruments (...</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40105</t>
+          <t>HGB-ANH-40131</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -14942,26 +15989,34 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Has a disclosure of stock movements / changes in inventories been made? (Vorratsbestandsveränderung)</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has a statement on the recognition and measurement of lease assets and liabilities been disclosed? (Leasingangaben)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has a statement on the recognition and measurement of lease ...</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40106</t>
+          <t>HGB-ANH-50002</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -14971,26 +16026,34 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Have other operating income (sonstige Erträge) been broken down by category? (Sonstige Erträge)</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has a statement on the assumption of going concern (Fortführung der Unternehmenstätigkeit) been disclosed? (Going-Concern-Annahme)</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has a statement on the assumption of going concern (Fortführ...</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40107</t>
+          <t>HGB-ANH-50003</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -15000,7 +16063,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Has research and development (Forschung und Entwicklung) expenditure been disclosed? (Forschungs- und Entwicklungskosten)</t>
+          <t>Has the balance sheet date (Bilanzstichtag) been disclosed? (Jahresabschlussstichtag)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -15015,15 +16078,19 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>R&amp;D not disclosed</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has the balance sheet date (Bilanzstichtag) been disclosed? ...</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40108</t>
+          <t>HGB-ANH-50004</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -15033,26 +16100,34 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Has a breakdown of material costs ( Materialaufwand) been disclosed? (Materialaufwand)</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has the legal form (Rechtsform) of the entity been disclosed? (Rechtsform)</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has the legal form (Rechtsform) of the entity been disclosed...</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40109</t>
+          <t>HGB-ANH-50005</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -15062,26 +16137,34 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Has a breakdown of personnel costs ( Personalaufwand) been disclosed? (Personalaufwand)</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has the company's registered office (Sitz der Gesellschaft) been disclosed? (Sitz der Gesellschaft)</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Has the company's registered office (Sitz der Gesellschaft) ...</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40119</t>
+          <t>HGB-ANH-50008</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -15091,7 +16174,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Has any significant uncalled capital (ausstehende Einlagen) been disclosed? (Nicht eingeforderte Einlagen)</t>
+          <t>Has membership of the Gesellschafterversammlung been disclosed? (Gesellschafter)</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -15106,15 +16189,19 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>No uncalled capital</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Has membership of the Gesellschafterversammlung been disclos...</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40125</t>
+          <t>HGB-ANH-50009</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -15124,7 +16211,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Have audit fees been broken down by activity (Abschlussprüferleistungen)? (Aufschlüsselung des Prüfungshonorars)</t>
+          <t>Have the members of the supervisory board (Aufsichtsrat) been disclosed? (Mitglieder des Aufsichtsrats)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -15139,54 +16226,66 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>No fee breakdown</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Have the members of the supervisory board (Aufsichtsrat) bee...</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40126</t>
+          <t>HGB-LAG-60001</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Anhang</t>
+          <t>Lagebericht</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Has a statement on the application of the simplification rule for deferred taxes (§274a HGB) been disclosed? ( Vereinfachungsregelung latente Steuern)</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht present the business progress (Geschäftsverlauf) including the business result (Geschäftsergebnis) in a manner that gives a true and fair view of the company's position?</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Mandatory item not found in FS: Does the Lagebericht present the business progress (Geschäft...</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40127</t>
+          <t>HGB-LAG-60002</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Anhang</t>
+          <t>Lagebericht</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Has a statement on the use of the exemption under §264 Abs. 3 HGB (small company relief) been made? (Handelsrechtliche Befreiung)</t>
+          <t>Does the Lagebericht present the Lage (position) of the capital company so that a true and fair view (den tatsächlichen Verhältnissen entsprechendes Bild) is conveyed?</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -15201,25 +16300,29 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>No small company</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Does the Lagebericht present the Lage (position) of the capi...</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40129</t>
+          <t>HGB-LAG-60004</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Anhang</t>
+          <t>Lagebericht</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Has information on the disaggregation of revenue (Umsatzzerlegung) been disclosed? (Umsatzzerlegung)</t>
+          <t>Does the Lagebericht include the most significant financial performance indicators (finanzielle Leistungsindikatoren) that are material to the business activities?</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -15234,25 +16337,29 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>No revenue split</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Does the Lagebericht include the most significant financial ...</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40130</t>
+          <t>HGB-LAG-60005</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Anhang</t>
+          <t>Lagebericht</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Has information on the fair value of financial instruments (Beizulegender Zeitwert) been disclosed? (Fair-Value-Angaben)</t>
+          <t>Are the financial performance indicators explained with reference to the amounts shown in the annual financial statements?</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -15267,25 +16374,29 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>No fair value</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Are the financial performance indicators explained with refe...</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40132</t>
+          <t>HGB-LAG-60015</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Anhang</t>
+          <t>Lagebericht</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Has information on the nature and extent of government grants (Investitionszulagen) been disclosed? (Zuwendungen der öffentlichen Hand)</t>
+          <t>Does the Lagebericht disclose existing branch offices (bestehende Zweigniederlassungen) of the company?</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -15300,631 +16411,14 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>No grants</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40133</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Has a statement on the underlying currency for significant transactions been disclosed? (Währungsangaben)</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>No currency</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40201</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Has the protective clause (Schutzklausel) under §286 HGB been invoked appropriately? (Befreiung von Einzelangaben)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-50008</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Has membership of the Gesellschafterversammlung been disclosed? (Gesellschafter)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Owner loan visible but full structure not</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-50103</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Has the entity disclosed the exercise of the 5-year exemption option for medium companies? (Fünf-Jahres-Befreiung)</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>No 5-year exemption</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60001</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht present the business progress (Geschäftsverlauf) including the business result (Geschäftsergebnis) in a manner that gives a true and fair view of the company's position?</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60002</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht present the Lage (position) of the capital company so that a true and fair view (den tatsächlichen Verhältnissen entsprechendes Bild) is conveyed?</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60003</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht contain a balanced and comprehensive analysis (ausgewogene und umfassende Analyse) appropriate to the scope and complexity of the business activities?</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60004</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht include the most significant financial performance indicators (finanzielle Leistungsindikatoren) that are material to the business activities?</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60005</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Are the financial performance indicators explained with reference to the amounts shown in the annual financial statements?</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60006</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht assess and explain the expected future development (voraussichtliche Entwicklung) including its material opportunities (Chancen) and risks (Risiken)?</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60007</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Are the underlying assumptions (Annahmen) for the expected development disclosed in the Lagebericht?</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60008</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose the risk management objectives and methods (Risikomanagementziele und -methoden) of the company?</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60009</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose the methods used to hedge all important types of transactions that are recognised in hedge accounting?</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60010</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose price change risks (Preisänderungsrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60011</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose default risks (Ausfallrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60012</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose liquidity risks (Liquiditätsrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60013</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose risks from payment flow fluctuations (Zahlungsstromschwankungen) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60014</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht include disclosure on the research and development area (Bereich Forschung und Entwicklung)?</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60015</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose existing branch offices (bestehende Zweigniederlassungen) of the company?</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60016</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht describe the essential features of the internal control system (wesentliche Merkmale des internen Kontrollsystems) in relation to the accounting process?</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60017</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht describe the essential features of the risk management system (wesentliche Merkmale des Risikomanagementsystems) in relation to the accounting process?</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>JUDGMENT_REQUIRED</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+          <t>Mandatory item not found in FS: Does the Lagebericht disclose existing branch offices (beste...</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Required but not found in extracted text</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/v2/output/results.xlsx
+++ b/v2/output/results.xlsx
@@ -36,7 +36,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,12 +59,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -107,9 +101,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -551,7 +542,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -561,7 +552,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -571,7 +562,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -581,7 +572,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -592,7 +583,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
     </row>
@@ -650,20 +641,20 @@
         <v>62</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -677,20 +668,20 @@
         <v>44</v>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -704,20 +695,20 @@
         <v>50</v>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -731,20 +722,20 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -911,11 +902,7 @@
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Page 3: Immaterielle Vermögensgegenstände EUR 278,004.50 disclosed under Anlagevermögen</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
@@ -962,18 +949,18 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Page 3: Immaterielle Vermögensgegenstände EUR 278,004.50 disclosed as single line under Anlagevermögen</t>
-        </is>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
@@ -1020,22 +1007,14 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>No Geschäfts- oder Firmenwert disclosed in Anlagevermögen</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
@@ -1082,18 +1061,18 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="n"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Page 3: geleistete Anzahlungen und Anlagen im Bau EUR 219,069.98 disclosed under Sachanlagen</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
@@ -1147,11 +1126,7 @@
       </c>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Page 3: Sachanlagen EUR 2,310,931.48 disclosed with all four categories</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
@@ -1198,18 +1173,18 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Page 3: Grundstücke, grundstücksgleiche Rechte und Bauten EUR 260,009 disclosed</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
@@ -1263,11 +1238,7 @@
       </c>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Page 3: technische Anlagen und Maschinen EUR 91,533 disclosed</t>
-        </is>
-      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
@@ -1321,11 +1292,7 @@
       </c>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Page 3: andere Anlagen, Betriebs- und Geschäftsausstattung EUR 1,740,319.50 disclosed</t>
-        </is>
-      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
@@ -1379,11 +1346,7 @@
       </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Page 3: geleistete Anzahlungen und Anlagen im Bau EUR 219,069.98 disclosed</t>
-        </is>
-      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
@@ -1437,11 +1400,7 @@
       </c>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Page 3: Finanzanlagen EUR 86,904 disclosed (Beteiligungen)</t>
-        </is>
-      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1488,22 +1447,14 @@
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>No separate Anteile an verbundenen Unternehmen disclosed - only Beteiligungen EUR 86,904 shown</t>
-        </is>
-      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
@@ -1561,11 +1512,7 @@
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>No Ausleihungen against affiliated companies disclosed in Finanzanlagen</t>
-        </is>
-      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
@@ -1612,22 +1559,14 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>No Wertpapiere des Anlagevermögens disclosed</t>
-        </is>
-      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
@@ -1685,11 +1624,7 @@
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>No sonstige Ausleihungen disclosed</t>
-        </is>
-      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -1743,11 +1678,7 @@
       </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Vorräte EUR 18,756,886.55 disclosed</t>
-        </is>
-      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
@@ -1805,11 +1736,7 @@
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Vorräte shown as single line EUR 18,756,886.55 - no breakdown into sub-categories</t>
-        </is>
-      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
@@ -1856,22 +1783,14 @@
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Vorräte shown as single line EUR 18,756,886.55 - no breakdown into sub-categories</t>
-        </is>
-      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -1918,22 +1837,14 @@
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Vorräte shown as single line EUR 18,756,886.55 - no breakdown into sub-categories</t>
-        </is>
-      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
@@ -1980,22 +1891,14 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Vorräte shown as single line EUR 18,756,886.55 - no breakdown into sub-categories</t>
-        </is>
-      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
@@ -2049,11 +1952,7 @@
       </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Forderungen und sonstige Vermögensgegenstände EUR 6,855,202.02 disclosed</t>
-        </is>
-      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
@@ -2100,22 +1999,14 @@
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Forderungen broken down by counterparty (Gesellschafter, Beteiligungsverhältnis) - no separate Forderungen aus Lieferungen und Leistungen line</t>
-        </is>
-      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
@@ -2169,11 +2060,7 @@
       </c>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Forderungen gegen Gesellschafter EUR 5,024,986.74 disclosed</t>
-        </is>
-      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
@@ -2227,11 +2114,7 @@
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Forderungen gegen Unternehmen mit Beteiligungsverhältnis EUR 15,367.05 disclosed</t>
-        </is>
-      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
@@ -2285,11 +2168,7 @@
       </c>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: sonstige Vermögensgegenstände EUR 1,814,848.23 disclosed</t>
-        </is>
-      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
@@ -2336,18 +2215,18 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Wertpapiere EUR 2,000 disclosed (shown as single line)</t>
-        </is>
-      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
@@ -2401,11 +2280,7 @@
       </c>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Kassenbestand, Bundesbankguthaben, Guthaben bei Kreditinstituten und Schecks EUR 194,604.57 disclosed</t>
-        </is>
-      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
@@ -2459,11 +2334,7 @@
       </c>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Rechnungsabgrenzungsposten EUR 61,169.78 disclosed</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
@@ -2510,22 +2381,14 @@
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>No aktive latente Steuern visible in Bilanz (amount is 0)</t>
-        </is>
-      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
@@ -2576,22 +2439,14 @@
           <t>If assets are offset against liabilities per §246 Abs. 2 HGB resulting in a net asset position</t>
         </is>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>No aktiver Unterschiedsbetrag disclosed</t>
-        </is>
-      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
@@ -2645,11 +2500,7 @@
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Eigenkapital properly structured with Gezeichnetes Kapital, Gewinnrücklagen, Gewinnvortrag, Bilanzgewinn</t>
-        </is>
-      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
@@ -2703,11 +2554,7 @@
       </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Gezeichnetes Kapital EUR 512,000 disclosed</t>
-        </is>
-      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
@@ -2761,11 +2608,7 @@
       </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Gewinnrücklagen EUR 450,000 disclosed (Kapitalrücklage combined with retained earnings)</t>
-        </is>
-      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
@@ -2819,11 +2662,7 @@
       </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Gewinnrücklagen EUR 450,000 disclosed as single line</t>
-        </is>
-      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
@@ -2870,22 +2709,14 @@
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Cannot determine gesetzliche Rücklage separately - Gewinnrücklagen shown as EUR 450,000</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
@@ -2936,22 +2767,14 @@
           <t>If the company holds shares in a controlling or majority-owned entity</t>
         </is>
       </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>No Rücklage für Anteile an herrschendem Unternehmen disclosed</t>
-        </is>
-      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
@@ -3013,11 +2836,7 @@
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>No satzungsmäßige Rücklagen disclosed separately</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
@@ -3071,11 +2890,7 @@
       </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: andere Gewinnrücklagen included in Gewinnrücklagen EUR 450,000</t>
-        </is>
-      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
@@ -3129,11 +2944,7 @@
       </c>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Gewinnvortrag EUR 15,967,079.87 disclosed</t>
-        </is>
-      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
@@ -3187,11 +2998,7 @@
       </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Jahresüberschuss EUR 301,937.27 disclosed</t>
-        </is>
-      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
@@ -3245,11 +3052,7 @@
       </c>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Rückstellungen EUR 1,956,451.58 disclosed (single line, no breakdown per §288)</t>
-        </is>
-      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
@@ -3296,22 +3099,14 @@
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Rückstellungen shown as single line - cannot determine pension provisions separately</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
@@ -3365,11 +3160,7 @@
       </c>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: pension provisions disclosed with Heubeck-Richttafeln 2018G, discount rate 1.82%</t>
-        </is>
-      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
@@ -3416,22 +3207,14 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Rückstellungen shown as single line EUR 1,956,451.58 - no separate Steuerrückstellungen visible</t>
-        </is>
-      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
@@ -3478,22 +3261,14 @@
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Rückstellungen shown as single line - no separate sonstige Rückstellungen visible</t>
-        </is>
-      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
@@ -3547,11 +3322,7 @@
       </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: Rückstellungen measured at Erfüllungsbetrag with prudent assessment</t>
-        </is>
-      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
@@ -3605,11 +3376,7 @@
       </c>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>Page 4-5: Verbindlichkeiten disclosed with categories</t>
-        </is>
-      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr"/>
@@ -3667,11 +3434,7 @@
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>No Anleihen disclosed</t>
-        </is>
-      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
@@ -3725,11 +3488,7 @@
       </c>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Verbindlichkeiten gegenüber Kreditinstituten EUR 7,253,591.71 disclosed</t>
-        </is>
-      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
@@ -3787,11 +3546,7 @@
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>No erhaltene Anzahlungen on balance sheet</t>
-        </is>
-      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
@@ -3838,22 +3593,14 @@
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Verbindlichkeiten shown as total - cannot isolate Verbindlichkeiten aus Lieferungen und Leistungen separately</t>
-        </is>
-      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr"/>
@@ -3911,11 +3658,7 @@
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>No Wechselverbindlichkeiten disclosed</t>
-        </is>
-      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr"/>
       <c r="P52" s="2" t="inlineStr"/>
@@ -3962,22 +3705,14 @@
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>No Verbindlichkeiten gegenüber verbundenen Unternehmen disclosed separately</t>
-        </is>
-      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr"/>
       <c r="P53" s="2" t="inlineStr"/>
@@ -4031,11 +3766,7 @@
       </c>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: Verbindlichkeiten gegenüber Unternehmen mit Beteiligungsverhältnis EUR 278,930.99 disclosed</t>
-        </is>
-      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr"/>
@@ -4089,11 +3820,7 @@
       </c>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: sonstige Verbindlichkeiten EUR 2,099,302.47 disclosed</t>
-        </is>
-      </c>
+      <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr"/>
       <c r="P55" s="2" t="inlineStr"/>
@@ -4147,11 +3874,7 @@
       </c>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: Rechnungsabgrenzungsposten (passiv) EUR 3,340 disclosed</t>
-        </is>
-      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr"/>
@@ -4198,22 +3921,14 @@
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>No passive latente Steuern visible in Bilanz</t>
-        </is>
-      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr"/>
       <c r="P57" s="2" t="inlineStr"/>
@@ -4267,11 +3982,7 @@
       </c>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Verbindlichkeiten with maturity breakdown disclosed (bis zu einem Jahr, mehr als ein Jahr)</t>
-        </is>
-      </c>
+      <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr"/>
       <c r="P58" s="2" t="inlineStr"/>
@@ -4325,11 +4036,7 @@
       </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: collateral disclosed - Sicherungsübereignung Warenlager EUR 18,392 for Kreditinstitute</t>
-        </is>
-      </c>
+      <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr"/>
       <c r="P59" s="2" t="inlineStr"/>
@@ -4383,11 +4090,7 @@
       </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>Page 4: Gezeichnetes Kapital EUR 512,000 disclosed, no changes in capital reserves visible</t>
-        </is>
-      </c>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="inlineStr"/>
@@ -4441,11 +4144,7 @@
       </c>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: Ergebnisverwendungsvorschlag - Jahresüberschuss to Gewinnvortrag</t>
-        </is>
-      </c>
+      <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr"/>
       <c r="P61" s="2" t="inlineStr"/>
@@ -4492,18 +4191,18 @@
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="n"/>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: secured liabilities disclosed - Sicherungsübereignung</t>
-        </is>
-      </c>
+      <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr"/>
@@ -4554,22 +4253,14 @@
           <t>Medium GmbH not providing detailed provision breakdown in Anhang</t>
         </is>
       </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr"/>
       <c r="P63" s="2" t="inlineStr"/>
@@ -4737,11 +4428,7 @@
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: Gliederung erfolgt gemäß §275 Abs. 1 HGB nach dem Gesamtkostenverfahren</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
@@ -4788,18 +4475,18 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht: Umsatzerlöse TEUR 20,489 (2023)</t>
-        </is>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
@@ -4853,11 +4540,7 @@
       </c>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Page 5 GuV: 1. Rohergebnis EUR 9,784,398.70 (includes Bestandsveränderung)</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
@@ -4904,22 +4587,14 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>No separate Andere aktivierte Eigenleistungen line visible in GuV</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
@@ -4966,18 +4641,18 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="n"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: Gesamtleistung shown as Rohergebnis EUR 9,784,398.70</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
@@ -5024,18 +4699,18 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Materialaufwand included in Rohergebnis - no separate line in GuV format shown</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
@@ -5089,11 +4764,7 @@
       </c>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 2. Personalaufwand EUR 4,186,545.21 disclosed</t>
-        </is>
-      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
@@ -5147,11 +4818,7 @@
       </c>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 3. Abschreibungen EUR 510,704.32 disclosed</t>
-        </is>
-      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
@@ -5205,11 +4872,7 @@
       </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 4. sonstige betriebliche Aufwendungen EUR 4,432,041.45 disclosed</t>
-        </is>
-      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
@@ -5263,11 +4926,7 @@
       </c>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Operating result implicit in EBIT TEUR 806 per Lagebericht</t>
-        </is>
-      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
@@ -5321,11 +4980,7 @@
       </c>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 5. Erträge aus Beteiligungen EUR 8,007 disclosed</t>
-        </is>
-      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
@@ -5372,22 +5027,14 @@
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>No separate Erträge aus anderen Wertpapieren und Ausleihungen line visible</t>
-        </is>
-      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
@@ -5441,11 +5088,7 @@
       </c>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 6. sonstige Zinsen und ähnliche Erträge EUR 179,710.83 disclosed</t>
-        </is>
-      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
@@ -5492,22 +5135,14 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>No separate Abschreibungen auf Finanzanlagen line visible</t>
-        </is>
-      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -5561,11 +5196,7 @@
       </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 7. Zinsen und ähnliche Aufwendungen EUR 457,906.42 disclosed</t>
-        </is>
-      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
@@ -5619,11 +5250,7 @@
       </c>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 8. Steuern vom Einkommen und vom Ertrag EUR 46,156.90 disclosed</t>
-        </is>
-      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
@@ -5677,11 +5304,7 @@
       </c>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 10. sonstige Steuern EUR 36,824.96 disclosed</t>
-        </is>
-      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -5735,11 +5358,7 @@
       </c>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Same as 30011 - Erträge aus Beteiligungen EUR 8,007</t>
-        </is>
-      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
@@ -5786,22 +5405,14 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>No Erträge aus Gewinnabführung visible</t>
-        </is>
-      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
@@ -5848,22 +5459,14 @@
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>No Verluste aus Gewinnabführung visible</t>
-        </is>
-      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
@@ -5917,11 +5520,7 @@
       </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 11. Jahresüberschuss EUR 301,937.27 disclosed</t>
-        </is>
-      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
@@ -5968,22 +5567,14 @@
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>Jahresüberschuss positive, no Jahresfehlbetrag</t>
-        </is>
-      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
@@ -6037,11 +5628,7 @@
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 12. Gewinnvortrag aus dem Vorjahr EUR 16,505,583.97 disclosed</t>
-        </is>
-      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
@@ -6088,22 +5675,14 @@
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>No Entnahme from reserves visible in GuV</t>
-        </is>
-      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
@@ -6150,22 +5729,14 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>No Einstellung in Gewinnrücklagen visible in GuV</t>
-        </is>
-      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
@@ -6219,11 +5790,7 @@
       </c>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: 13. Bilanzgewinn EUR 15,967,079.87 disclosed</t>
-        </is>
-      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
@@ -6270,22 +5837,14 @@
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>Bilanzgewinn positive, no Bilanzverlust</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
@@ -6332,22 +5891,18 @@
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>Kontenplan not included in PDF financial statements</t>
-        </is>
-      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
@@ -6394,18 +5949,18 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="n"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>Page 3-5 Bilanz and GuV show prior year figures (Vorjahr EUR column)</t>
-        </is>
-      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
@@ -6467,11 +6022,7 @@
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>No reclassifications disclosed</t>
-        </is>
-      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
@@ -6522,7 +6073,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J32" s="6" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6533,11 +6084,7 @@
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
@@ -6588,7 +6135,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J33" s="6" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6599,11 +6146,7 @@
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
@@ -6654,7 +6197,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J34" s="6" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6665,11 +6208,7 @@
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
@@ -6720,7 +6259,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J35" s="6" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6731,11 +6270,7 @@
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
@@ -6786,7 +6321,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J36" s="6" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6797,11 +6332,7 @@
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
@@ -6852,7 +6383,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J37" s="6" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6863,11 +6394,7 @@
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
@@ -6918,22 +6445,18 @@
           <t>If disclosure is not prohibited by §286 Abs. 2 and would not cause significant harm to the company</t>
         </is>
       </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>EXEMPTION_CLAIMED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 - no revenue breakdown by activity</t>
-        </is>
-      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
@@ -6984,22 +6507,18 @@
           <t>If disclosure is not prohibited by §286 Abs. 2 and would not cause significant harm to the company</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>EXEMPTION_CLAIMED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 - no revenue breakdown by geography</t>
-        </is>
-      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
@@ -7061,11 +6580,7 @@
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>No explicit §286 Abs. 2 protective clause invocation for revenue breakdown</t>
-        </is>
-      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
@@ -7116,18 +6631,18 @@
           <t>If two of three thresholds exceeded: €12M revenue, €6M assets, 50 employees</t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="n"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: mittelgroße Kapitalgesellschaft i.S.d. §267 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
@@ -7178,7 +6693,7 @@
           <t>If §288 Abs. 2 applies (medium-sized GmbH)</t>
         </is>
       </c>
-      <c r="J42" s="6" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7189,11 +6704,7 @@
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
@@ -7240,18 +6751,18 @@
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht included (page 1-2 of PDF)</t>
-        </is>
-      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
@@ -7298,18 +6809,18 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="n"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Page 5: GuV presented in vertical format with all mandatory line items</t>
-        </is>
-      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
@@ -7356,18 +6867,18 @@
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="n"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>No material netting visible - items shown separately</t>
-        </is>
-      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
@@ -7528,18 +7039,18 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: Bilanzierungs- und Bewertungsmethoden disclosed</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
@@ -7586,18 +7097,18 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: Bewertung Warenbestand angepasst - change disclosed</t>
-        </is>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
@@ -7655,11 +7166,7 @@
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>No material estimate changes disclosed</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
@@ -7717,11 +7224,7 @@
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>No subsidiary information disclosed</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
@@ -7779,11 +7282,7 @@
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>No equity of subsidiaries disclosed</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
@@ -7830,18 +7329,18 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>No Konzernabschluss prepared - size qualifies for exemption</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
@@ -7892,7 +7391,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7903,11 +7402,7 @@
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
@@ -7954,18 +7449,18 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: Vorräte with groups Bewertung disclosed</t>
-        </is>
-      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
@@ -8019,11 +7514,7 @@
       </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: detailed methods disclosed for Bewertung</t>
-        </is>
-      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
@@ -8081,11 +7572,7 @@
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>No separate F&amp;E Kosten disclosed</t>
-        </is>
-      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
@@ -8136,7 +7623,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8147,11 +7634,7 @@
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
@@ -8202,7 +7685,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8213,11 +7696,7 @@
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
@@ -8264,18 +7743,18 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="n"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: Abschreibungen linear, Nutzungsdauer disclosed</t>
-        </is>
-      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
@@ -8329,11 +7808,7 @@
       </c>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: Forderungen/Verbindlichkeiten against Beteiligungsverhältnis disclosed</t>
-        </is>
-      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -8387,11 +7862,7 @@
       </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: Mietverpflichtungen EUR 2,076,950, Leasing EUR 238,635.72 disclosed</t>
-        </is>
-      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
@@ -8449,11 +7920,7 @@
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>No prior year restatements disclosed</t>
-        </is>
-      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
@@ -8511,11 +7978,7 @@
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>No subsequent events disclosed</t>
-        </is>
-      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -8562,18 +8025,18 @@
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="n"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: Durchschnittszahl 63 (49 Angestellte, 14 gewerbliche)</t>
-        </is>
-      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
@@ -8620,18 +8083,18 @@
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: Durchschnittszahl 63 (49 Angestellte, 14 gewerbliche)</t>
-        </is>
-      </c>
+      <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr"/>
       <c r="P20" s="2" t="inlineStr"/>
@@ -8678,18 +8141,18 @@
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="n"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: Bezüge der Geschäftsführer uses §286 Abs. 4 Schutzrecht</t>
-        </is>
-      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="inlineStr"/>
@@ -8740,7 +8203,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8751,11 +8214,7 @@
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr"/>
@@ -8813,11 +8272,7 @@
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>No share-based payment disclosed</t>
-        </is>
-      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr"/>
       <c r="P23" s="2" t="inlineStr"/>
@@ -8871,11 +8326,7 @@
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>No uncalled capital disclosed (all paid)</t>
-        </is>
-      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="inlineStr"/>
@@ -8933,11 +8384,7 @@
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>No parent company disclosed</t>
-        </is>
-      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr"/>
       <c r="P25" s="2" t="inlineStr"/>
@@ -8988,7 +8435,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J26" s="6" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8999,11 +8446,7 @@
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr"/>
@@ -9061,11 +8504,7 @@
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>No group entities disclosed</t>
-        </is>
-      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="inlineStr"/>
@@ -9123,11 +8562,7 @@
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>No branch offices disclosed</t>
-        </is>
-      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr"/>
       <c r="P28" s="2" t="inlineStr"/>
@@ -9181,11 +8616,7 @@
       </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>Page 6 Anhang: Pensionsverpflichtungen with Heubeck-Richttafeln 2018G, 1.82% disclosed</t>
-        </is>
-      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="inlineStr"/>
@@ -9243,11 +8674,7 @@
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>No breakdown of auditor fees</t>
-        </is>
-      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="inlineStr"/>
@@ -9294,22 +8721,14 @@
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>No simplified deferred tax statement</t>
-        </is>
-      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr"/>
       <c r="P31" s="2" t="inlineStr"/>
@@ -9367,11 +8786,7 @@
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>No §264 Abs. 3 exemption disclosed</t>
-        </is>
-      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr"/>
@@ -9429,11 +8844,7 @@
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>No Bewertungseinheiten disclosed</t>
-        </is>
-      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="inlineStr"/>
@@ -9484,7 +8895,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J34" s="6" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9495,11 +8906,7 @@
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr"/>
       <c r="P34" s="2" t="inlineStr"/>
@@ -9546,22 +8953,14 @@
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>No fair value disclosures for financial instruments</t>
-        </is>
-      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="inlineStr"/>
@@ -9608,18 +9007,18 @@
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="n"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: Leasingverträge EUR 238,635.72 disclosed</t>
-        </is>
-      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="inlineStr"/>
@@ -9670,7 +9069,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J37" s="6" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9681,11 +9080,7 @@
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr"/>
       <c r="P37" s="2" t="inlineStr"/>
@@ -9732,18 +9127,18 @@
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>Page 7 Anhang: Währungsrisiko USD disclosed</t>
-        </is>
-      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr"/>
       <c r="P38" s="2" t="inlineStr"/>
@@ -9794,22 +9189,18 @@
           <t>Entity claims §286 exemption for specific disclosures</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>EXEMPTION_CLAIMED</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="inlineStr"/>
@@ -9863,11 +9254,7 @@
       </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>Page 6-7 Anhang: all mandatory §287 requirements met</t>
-        </is>
-      </c>
+      <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr"/>
@@ -9914,18 +9301,18 @@
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="n"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>Going concern assumed - no uncertainties disclosed</t>
-        </is>
-      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr"/>
       <c r="P41" s="2" t="inlineStr"/>
@@ -9979,11 +9366,7 @@
       </c>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>Page 1: Bilanzstichtag 31.12.2023 disclosed</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="inlineStr"/>
@@ -10030,18 +9413,18 @@
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>Legal form GmbH disclosed in header</t>
-        </is>
-      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr"/>
       <c r="P43" s="2" t="inlineStr"/>
@@ -10095,11 +9478,7 @@
       </c>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>Page 1: Schwäbisch Gmünd disclosed as registered office</t>
-        </is>
-      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="inlineStr"/>
@@ -10146,18 +9525,18 @@
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="n"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>Page 1: HiFi-Produkte described in Lagebericht</t>
-        </is>
-      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr"/>
@@ -10204,18 +9583,18 @@
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>Page 7: Geschäftsführer Günther Nubert, Markus Pedal, Daniel T. Schütze disclosed</t>
-        </is>
-      </c>
+      <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr"/>
       <c r="P46" s="2" t="inlineStr"/>
@@ -10269,11 +9648,7 @@
       </c>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>Forderungen gegen Gesellschafter disclosed - shows shareholder relationship</t>
-        </is>
-      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr"/>
       <c r="P47" s="2" t="inlineStr"/>
@@ -10331,11 +9706,7 @@
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>No Aufsichtsrat - not required for GmbH under 500 employees</t>
-        </is>
-      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="inlineStr"/>
@@ -10386,7 +9757,7 @@
           <t>Entity claims §288 Abs. 2 exemption</t>
         </is>
       </c>
-      <c r="J49" s="6" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10397,11 +9768,7 @@
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr"/>
       <c r="P49" s="2" t="inlineStr"/>
@@ -10452,7 +9819,7 @@
           <t>Entity claims §288 Abs. 2 exemption</t>
         </is>
       </c>
-      <c r="J50" s="6" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10463,11 +9830,7 @@
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="inlineStr"/>
@@ -10518,7 +9881,7 @@
           <t>Entity invokes 5-year exemption under §288 Abs. 1</t>
         </is>
       </c>
-      <c r="J51" s="6" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10529,11 +9892,7 @@
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
-        </is>
-      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="inlineStr"/>
@@ -10694,22 +10053,18 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
@@ -10756,22 +10111,14 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="2" t="inlineStr"/>
@@ -10818,22 +10165,18 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
@@ -10880,22 +10223,18 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr"/>
@@ -10942,22 +10281,18 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr"/>
       <c r="P6" s="2" t="inlineStr"/>
@@ -11004,22 +10339,18 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M7" s="2" t="inlineStr"/>
       <c r="N7" s="2" t="inlineStr"/>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
@@ -11066,22 +10397,18 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="inlineStr"/>
@@ -11128,22 +10455,18 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
@@ -11194,22 +10517,18 @@
           <t>If the company uses hedge accounting (Bilanzierung von Sicherungsgeschäften)</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
@@ -11260,22 +10579,18 @@
           <t>If price change risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr"/>
       <c r="P11" s="2" t="inlineStr"/>
@@ -11326,22 +10641,18 @@
           <t>If default risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
@@ -11392,22 +10703,18 @@
           <t>If liquidity risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="2" t="inlineStr"/>
@@ -11458,22 +10765,18 @@
           <t>If cash flow fluctuation risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="inlineStr"/>
@@ -11520,22 +10823,18 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
@@ -11582,22 +10881,18 @@
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr"/>
       <c r="P16" s="2" t="inlineStr"/>
@@ -11648,22 +10943,18 @@
           <t>If the company is a capital market oriented company (§ 264d HGB - Kapitalmarktorientierte Kapitalgesellschaft)</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="inlineStr"/>
@@ -11714,22 +11005,18 @@
           <t>If the company is a capital market oriented company (§ 264d HGB - Kapitalmarktorientierte Kapitalgesellschaft)</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
+          <t>MISSING_EVIDENCE</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="inlineStr"/>
@@ -11745,7 +11032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11797,7 +11084,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10003</t>
+          <t>HGB-BIL-10002</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -11807,7 +11094,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Is Geschäfts- oder Firmenwert (goodwill) from business combinations separately recognised and amortised over useful life?</t>
+          <t>Is selbst geschaffene gewerbliche Schutzrechte (self-created industrial property rights) disclosed separately from entgeltlich erworbene (acquired) items?</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -11820,17 +11107,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>No Geschäfts- oder Firmenwert disclosed in Anlagevermögen</t>
-        </is>
-      </c>
+      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10011</t>
+          <t>HGB-BIL-10004</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -11840,7 +11123,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Are Anteile an verbundenen Unternehmen (shares in affiliated companies) disclosed separately from Beteiligungen (participations)?</t>
+          <t>Are geleistete Anzahlungen on intangible assets disclosed as prepayments on non-current assets?</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -11853,17 +11136,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>No separate Anteile an verbundenen Unternehmen disclosed - only Beteiligungen EUR 86,904 shown</t>
-        </is>
-      </c>
+      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10012</t>
+          <t>HGB-BIL-10006</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -11873,7 +11152,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Are Ausleihungen (loans) to affiliated companies and to companies with participation interests disclosed separately from equity items?</t>
+          <t>Are Grundstücke und grundstücksgleiche Rechte (land and land rights) including buildings on third-party land disclosed separately?</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -11886,17 +11165,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>No Ausleihungen against affiliated companies disclosed in Finanzanlagen</t>
-        </is>
-      </c>
+      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10013</t>
+          <t>HGB-BIL-10012</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -11906,7 +11181,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Are Wertpapiere des Anlagevermögens (securities held as non-current assets) disclosed separately from current portfolio?</t>
+          <t>Are Ausleihungen (loans) to affiliated companies and to companies with participation interests disclosed separately from equity items?</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -11919,11 +11194,7 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>No Wertpapiere des Anlagevermögens disclosed</t>
-        </is>
-      </c>
+      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
@@ -11952,11 +11223,7 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>No sonstige Ausleihungen disclosed</t>
-        </is>
-      </c>
+      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
@@ -11985,17 +11252,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Vorräte shown as single line EUR 18,756,886.55 - no breakdown into sub-categories</t>
-        </is>
-      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10022</t>
+          <t>HGB-BIL-10030</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -12005,7 +11268,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Are unfertige Erzeugnisse and unfertige Leistungen (work in progress and services not yet billed) disclosed together?</t>
+          <t>Are Wertpapiere (securities) classified in current assets split into shares in affiliates and other securities?</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -12018,17 +11281,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Vorräte shown as single line EUR 18,756,886.55 - no breakdown into sub-categories</t>
-        </is>
-      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10023</t>
+          <t>HGB-BIL-20007</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -12038,7 +11297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Are finished goods and merchandise (fertige Erzeugnisse und Waren) disclosed as a single line item?</t>
+          <t>Are satzungsmäßige Rücklagen (statutory reserves per articles of association) disclosed separately?</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -12051,17 +11310,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Vorräte shown as single line EUR 18,756,886.55 - no breakdown into sub-categories</t>
-        </is>
-      </c>
+      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10024</t>
+          <t>HGB-BIL-20021</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -12071,7 +11326,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Are prepayments on inventory (geleistete Anzahlungen) disclosed as the final inventory line?</t>
+          <t>Are Anleihen (bonds) disclosed, with a sub-row showing the convertible portion if applicable?</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -12084,17 +11339,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Vorräte shown as single line EUR 18,756,886.55 - no breakdown into sub-categories</t>
-        </is>
-      </c>
+      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10026</t>
+          <t>HGB-BIL-20023</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -12104,7 +11355,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Are Forderungen aus Lieferungen und Leistungen (trade receivables) disclosed separately?</t>
+          <t>Are erhaltene Anzahlungen auf Bestellungen (advance payments received on orders) disclosed separately?</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -12117,17 +11368,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Forderungen broken down by counterparty (Gesellschafter, Beteiligungsverhältnis) - no separate Forderungen aus Lieferungen und Leistungen line</t>
-        </is>
-      </c>
+      <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10033</t>
+          <t>HGB-BIL-20025</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -12137,7 +11384,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Are aktive latente Steuern (deferred tax assets) disclosed as a separate posten under asset side?</t>
+          <t>Are liabilities from accepted drafts (Wechselverbindlichkeiten) disclosed separately?</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -12150,17 +11397,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>No aktive latente Steuern visible in Bilanz (amount is 0)</t>
-        </is>
-      </c>
+      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-10034</t>
+          <t>HGB-BIL-20035</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -12170,7 +11413,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Is aktiver Unterschiedsbetrag aus der Vermögensverrechnung (asset difference from asset offsetting) disclosed separately?</t>
+          <t>Is the total amount of liabilities secured by collateral (Pfandbriefe, etc.) disclosed per §285 No. 3a?</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -12183,60 +11426,52 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>No aktiver Unterschiedsbetrag disclosed</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20005</t>
+          <t>HGB-GUV-30002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Is the gesetzliche Rücklage (legal reserve) disclosed separately and is the required 10% of subscribed capital maintained?</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Revenue (Umsatzerlöse) - Line item 1 of Gesamtkostenverfahren</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Cannot determine gesetzliche Rücklage separately - Gewinnrücklagen shown as EUR 450,000</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20006</t>
+          <t>HGB-GUV-30005</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Is Rücklage für Anteile an einem herrschenden oder mehrheitlich beteiligten Unternehmen (reserve for shares in controlling company) disclosed if applicable?</t>
+          <t>Total operating performance (Gesamtleistung) - Calculated from lines 1-3</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -12249,27 +11484,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>No Rücklage für Anteile an herrschendem Unternehmen disclosed</t>
-        </is>
-      </c>
+      <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20007</t>
+          <t>HGB-GUV-30006</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Are satzungsmäßige Rücklagen (statutory reserves per articles of association) disclosed separately?</t>
+          <t>Cost of materials (Materialaufwand) - Line item 4</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -12282,126 +11513,110 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>No satzungsmäßige Rücklagen disclosed separately</t>
-        </is>
-      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20012</t>
+          <t>HGB-GUV-30030</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Are Rückstellungen für Pensionen und ähnliche Verpflichtungen (pension provisions and similar obligations) disclosed separately?</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the entity have a chart of accounts (Kontenplan) that maps to the Gesamtkostenverfahren line items per §275 Abs. 2 HGB?</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Rückstellungen shown as single line - cannot determine pension provisions separately</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20014</t>
+          <t>HGB-GUV-30031</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Are Steuerrückstellungen (tax provisions) disclosed as a separate line item?</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Are comparative figures for the prior financial year disclosed in the GuV per §275 Abs. 3 HGB?</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Rückstellungen shown as single line EUR 1,956,451.58 - no separate Steuerrückstellungen visible</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20015</t>
+          <t>HGB-GUV-30032</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Are sonstige Rückstellungen (other provisions) disclosed as the final provisions line, including all non-pension/tax provisions?</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Are items in the GuV presented in accordance with the prior year's classification if any material changes in business activities require reclassification per §275 Abs. 4 HGB?</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Rückstellungen shown as single line - no separate sonstige Rückstellungen visible</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20021</t>
+          <t>HGB-GUV-30060</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Are Anleihen (bonds) disclosed, with a sub-row showing the convertible portion if applicable?</t>
+          <t>Is revenue broken down by business activity (Tätigkeit) per §285 Nr. 14 HGB?</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -12414,27 +11629,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>No Anleihen disclosed</t>
-        </is>
-      </c>
+      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20023</t>
+          <t>HGB-GUV-30061</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Are erhaltene Anzahlungen auf Bestellungen (advance payments received on orders) disclosed separately?</t>
+          <t>Is revenue broken down by geographic market ( Märkte) per §285 Nr. 14 HGB?</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -12447,60 +11658,52 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>No erhaltene Anzahlungen on balance sheet</t>
-        </is>
-      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20024</t>
+          <t>HGB-GUV-30070</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Are Verbindlichkeiten aus Lieferungen und Leistungen (trade payables) disclosed separately?</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>If revenue breakdown by activity or geography is not disclosed, has the entity invoked the protective clause under §286 Abs. 2 HGB?</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Verbindlichkeiten shown as total - cannot isolate Verbindlichkeiten aus Lieferungen und Leistungen separately</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20025</t>
+          <t>HGB-GUV-30080</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Are liabilities from accepted drafts (Wechselverbindlichkeiten) disclosed separately?</t>
+          <t>Is the entity eligible for exemptions under §288 Abs. 2 HGB for medium-sized GmbH?</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -12513,27 +11716,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>No Wechselverbindlichkeiten disclosed</t>
-        </is>
-      </c>
+      <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20026</t>
+          <t>HGB-GUV-30082</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Are Verbindlichkeiten gegenüber verbundenen Unternehmen (payables to affiliated companies) disclosed separately?</t>
+          <t>Is the entity required to provide a management report (Lagebericht) despite being medium-sized under §289 HGB?</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -12546,27 +11745,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>No Verbindlichkeiten gegenüber verbundenen Unternehmen disclosed separately</t>
-        </is>
-      </c>
+      <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HGB-BIL-20030</t>
+          <t>HGB-GUV-30090</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Bilanz</t>
+          <t>GuV</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Are passive latente Steuern (deferred tax liabilities) disclosed as the final liability item?</t>
+          <t>Is there a clear presentation of the GuV using the vertically aligned format per §275 Abs. 1 HGB?</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -12579,17 +11774,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>No passive latente Steuern visible in Bilanz</t>
-        </is>
-      </c>
+      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30004</t>
+          <t>HGB-GUV-30091</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -12599,7 +11790,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Other own work capitalized (Andere aktivierte Eigenleistungen) - Line item 3</t>
+          <t>Are material items in the GuV not netted but shown separately per §265 Abs. 7 HGB?</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -12612,27 +11803,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>No separate Andere aktivierte Eigenleistungen line visible in GuV</t>
-        </is>
-      </c>
+      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30012</t>
+          <t>HGB-ANH-40001</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Income from other securities and loans (Erträge aus anderen Wertpapieren und Ausleihungen des Finanzanlagevermögens) - Line item 9</t>
+          <t>Have the accounting and valuation methods used been disclosed? (Bilanzierungsmethoden)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -12645,27 +11832,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>No separate Erträge aus anderen Wertpapieren und Ausleihungen line visible</t>
-        </is>
-      </c>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30014</t>
+          <t>HGB-ANH-40002</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Depreciation and amortization of financial assets and securities (Abschreibungen auf Finanzanlagen und auf Wertpapiere des Umlaufvermögens) - Line item 11</t>
+          <t>Have any changes to accounting and valuation methods been disclosed with justification? (Änderung der Bilanzierungsmethoden)</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -12678,27 +11861,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>No separate Abschreibungen auf Finanzanlagen line visible</t>
-        </is>
-      </c>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30019</t>
+          <t>HGB-ANH-40003</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Income from profit pooling, profit transfer or partial profit transfer agreements (Erträge aus Gewinnabführung) - Line item 15</t>
+          <t>Has the impact of any material changes in estimates been disclosed? (Wesentliche Schätzungsänderungen)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -12711,27 +11890,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>No Erträge aus Gewinnabführung visible</t>
-        </is>
-      </c>
+      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30020</t>
+          <t>HGB-ANH-40101</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Expenses from loss absorption (Verluste aus Gewinnabführung) - Line item 16</t>
+          <t>Has the name and registered office of subsidiaries been disclosed? (Name und Sitz von Tochterunternehmen)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -12744,27 +11919,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>No Verluste aus Gewinnabführung visible</t>
-        </is>
-      </c>
+      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30022</t>
+          <t>HGB-ANH-40102</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Net loss (Jahresfehlbetrag) - Line item 18</t>
+          <t>Has the equity ( Eigenkapital) of subsidiaries been disclosed? (Eigenkapital der Tochterunternehmen)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -12777,27 +11948,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Jahresüberschuss positive, no Jahresfehlbetrag</t>
-        </is>
-      </c>
+      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30024</t>
+          <t>HGB-ANH-40103</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Appropriation to other revenue reserves (Entnahme aus der Kapitalrücklage, Entnahme aus Gewinnrücklagen) - Line item 20</t>
+          <t>Has an exemption from preparing consolidated accounts (Konzernabschluss) been disclosed with reasons and criteria? (Befreiung von Konzernabschluss)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -12810,27 +11977,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>No Entnahme from reserves visible in GuV</t>
-        </is>
-      </c>
+      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30025</t>
+          <t>HGB-ANH-40105</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Appropriation to other revenue reserves (Einstellung in Gewinnrücklagen) - Line item 20 alternative</t>
+          <t>Has a disclosure of stock movements / changes in inventories been made? (Vorratsbestandsveränderung)</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -12843,27 +12006,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>No Einstellung in Gewinnrücklagen visible in GuV</t>
-        </is>
-      </c>
+      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30027</t>
+          <t>HGB-ANH-40107</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Uncovered loss (Bilanzverlust) - Line item 21 alternative</t>
+          <t>Has research and development (Forschung und Entwicklung) expenditure been disclosed? (Forschungs- und Entwicklungskosten)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -12876,60 +12035,52 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Bilanzgewinn positive, no Bilanzverlust</t>
-        </is>
-      </c>
+      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30030</t>
+          <t>HGB-ANH-40110</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Does the entity have a chart of accounts (Kontenplan) that maps to the Gesamtkostenverfahren line items per §275 Abs. 2 HGB?</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Have depreciation and amortization methods and periods been disclosed? (Abschreibungsmethoden)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Kontenplan not included in PDF financial statements</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30032</t>
+          <t>HGB-ANH-40113</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Are items in the GuV presented in accordance with the prior year's classification if any material changes in business activities require reclassification per §275 Abs. 4 HGB?</t>
+          <t>Have any restatements of prior year figures (Rückwirkung von Bilanzänderungen) been disclosed? (Rückwirkende Änderungen)</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -12942,27 +12093,23 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>No reclassifications disclosed</t>
-        </is>
-      </c>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HGB-GUV-30070</t>
+          <t>HGB-ANH-40114</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>GuV</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>If revenue breakdown by activity or geography is not disclosed, has the entity invoked the protective clause under §286 Abs. 2 HGB?</t>
+          <t>Have subsequent events (nachträgliche Ereignisse) after the balance sheet date been disclosed? (Nachtragsbericht)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -12975,17 +12122,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>No explicit §286 Abs. 2 protective clause invocation for revenue breakdown</t>
-        </is>
-      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40003</t>
+          <t>HGB-ANH-40115</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -12995,7 +12138,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Has the impact of any material changes in estimates been disclosed? (Wesentliche Schätzungsänderungen)</t>
+          <t>Has the average number of employees (Durchschnittszahl der Beschäftigten) been disclosed? (Beschäftigtenzahl)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -13008,17 +12151,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>No material estimate changes disclosed</t>
-        </is>
-      </c>
+      <c r="F38" s="2" t="inlineStr"/>
       <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40101</t>
+          <t>HGB-ANH-40115</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -13028,7 +12167,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Has the name and registered office of subsidiaries been disclosed? (Name und Sitz von Tochterunternehmen)</t>
+          <t>Have audit fees (Honorar des Abschlussprüfers) for the auditor been disclosed? (Abschlussprüferhonorar)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -13041,17 +12180,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>No subsidiary information disclosed</t>
-        </is>
-      </c>
+      <c r="F39" s="2" t="inlineStr"/>
       <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40102</t>
+          <t>HGB-ANH-40116</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -13061,7 +12196,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Has the equity ( Eigenkapital) of subsidiaries been disclosed? (Eigenkapital der Tochterunternehmen)</t>
+          <t>Has management remuneration (Vorstands-/Geschäftsführungsvergütung) been disclosed individually or in aggregate? (Gesamtbezüge der Organmitglieder)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -13074,17 +12209,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>No equity of subsidiaries disclosed</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40107</t>
+          <t>HGB-ANH-40118</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -13094,7 +12225,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Has research and development (Forschung und Entwicklung) expenditure been disclosed? (Forschungs- und Entwicklungskosten)</t>
+          <t>Has any share-based payment (aktienbasierte Vergütung) been disclosed? (Aktienbasierte Vergütung)</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -13107,17 +12238,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>No separate F&amp;E Kosten disclosed</t>
-        </is>
-      </c>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40113</t>
+          <t>HGB-ANH-40120</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -13127,7 +12254,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Have any restatements of prior year figures (Rückwirkung von Bilanzänderungen) been disclosed? (Rückwirkende Änderungen)</t>
+          <t>Has parent company information (Mutterunternehmen) been disclosed? (Mutterunternehmen)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -13140,17 +12267,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>No prior year restatements disclosed</t>
-        </is>
-      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40114</t>
+          <t>HGB-ANH-40122</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -13160,7 +12283,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Have subsequent events (nachträgliche Ereignisse) after the balance sheet date been disclosed? (Nachtragsbericht)</t>
+          <t>Has information on consolidated entities (Konsolidierungskreis) been disclosed? (Tochterunternehmen im Konzernabschluss)</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -13173,17 +12296,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>No subsequent events disclosed</t>
-        </is>
-      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40118</t>
+          <t>HGB-ANH-40123</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -13193,7 +12312,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Has any share-based payment (aktienbasierte Vergütung) been disclosed? (Aktienbasierte Vergütung)</t>
+          <t>Has information on branch offices (Zweigniederlassungen) been disclosed? (Zweigniederlassungen)</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -13206,17 +12325,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>No share-based payment disclosed</t>
-        </is>
-      </c>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40120</t>
+          <t>HGB-ANH-40125</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -13226,7 +12341,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Has parent company information (Mutterunternehmen) been disclosed? (Mutterunternehmen)</t>
+          <t>Have audit fees been broken down by activity (Abschlussprüferleistungen)? (Aufschlüsselung des Prüfungshonorars)</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -13239,17 +12354,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>No parent company disclosed</t>
-        </is>
-      </c>
+      <c r="F45" s="2" t="inlineStr"/>
       <c r="G45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40122</t>
+          <t>HGB-ANH-40127</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -13259,7 +12370,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Has information on consolidated entities (Konsolidierungskreis) been disclosed? (Tochterunternehmen im Konzernabschluss)</t>
+          <t>Has a statement on the use of the exemption under §264 Abs. 3 HGB (small company relief) been made? (Handelsrechtliche Befreiung)</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -13272,17 +12383,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>No group entities disclosed</t>
-        </is>
-      </c>
+      <c r="F46" s="2" t="inlineStr"/>
       <c r="G46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40123</t>
+          <t>HGB-ANH-40128</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -13292,7 +12399,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Has information on branch offices (Zweigniederlassungen) been disclosed? (Zweigniederlassungen)</t>
+          <t>Has the disclosure of financial instruments at fair value (Bewertungseinheiten) been made? (Bewertungseinheiten)</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -13305,17 +12412,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>No branch offices disclosed</t>
-        </is>
-      </c>
+      <c r="F47" s="2" t="inlineStr"/>
       <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40125</t>
+          <t>HGB-ANH-40131</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -13325,7 +12428,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Have audit fees been broken down by activity (Abschlussprüferleistungen)? (Aufschlüsselung des Prüfungshonorars)</t>
+          <t>Has a statement on the recognition and measurement of lease assets and liabilities been disclosed? (Leasingangaben)</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -13338,17 +12441,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>No breakdown of auditor fees</t>
-        </is>
-      </c>
+      <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40126</t>
+          <t>HGB-ANH-40133</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -13358,7 +12457,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Has a statement on the application of the simplification rule for deferred taxes (§274a HGB) been disclosed? ( Vereinfachungsregelung latente Steuern)</t>
+          <t>Has a statement on the underlying currency for significant transactions been disclosed? (Währungsangaben)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -13371,17 +12470,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>No simplified deferred tax statement</t>
-        </is>
-      </c>
+      <c r="F49" s="2" t="inlineStr"/>
       <c r="G49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40127</t>
+          <t>HGB-ANH-40201</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -13391,7 +12486,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Has a statement on the use of the exemption under §264 Abs. 3 HGB (small company relief) been made? (Handelsrechtliche Befreiung)</t>
+          <t>Has the protective clause (Schutzklausel) under §286 HGB been invoked appropriately? (Befreiung von Einzelangaben)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -13404,17 +12499,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>No §264 Abs. 3 exemption disclosed</t>
-        </is>
-      </c>
+      <c r="F50" s="2" t="inlineStr"/>
       <c r="G50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40128</t>
+          <t>HGB-ANH-50002</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -13424,7 +12515,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Has the disclosure of financial instruments at fair value (Bewertungseinheiten) been made? (Bewertungseinheiten)</t>
+          <t>Has a statement on the assumption of going concern (Fortführung der Unternehmenstätigkeit) been disclosed? (Going-Concern-Annahme)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -13437,17 +12528,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>No Bewertungseinheiten disclosed</t>
-        </is>
-      </c>
+      <c r="F51" s="2" t="inlineStr"/>
       <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-40130</t>
+          <t>HGB-ANH-50004</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -13457,7 +12544,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Has information on the fair value of financial instruments (Beizulegender Zeitwert) been disclosed? (Fair-Value-Angaben)</t>
+          <t>Has the legal form (Rechtsform) of the entity been disclosed? (Rechtsform)</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -13470,17 +12557,13 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>No fair value disclosures for financial instruments</t>
-        </is>
-      </c>
+      <c r="F52" s="2" t="inlineStr"/>
       <c r="G52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>HGB-ANH-50009</t>
+          <t>HGB-ANH-50006</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -13490,7 +12573,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Have the members of the supervisory board (Aufsichtsrat) been disclosed? (Mitglieder des Aufsichtsrats)</t>
+          <t>Has the company's object (Unternehmensgegenstand) been disclosed? (Gegenstand des Unternehmens)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -13503,83 +12586,71 @@
           <t>MISSING_EVIDENCE</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>No Aufsichtsrat - not required for GmbH under 500 employees</t>
-        </is>
-      </c>
+      <c r="F53" s="2" t="inlineStr"/>
       <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60001</t>
+          <t>HGB-ANH-50007</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Lagebericht</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht present the business progress (Geschäftsverlauf) including the business result (Geschäftsergebnis) in a manner that gives a true and fair view of the company's position?</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Has a list of managing directors (Geschäftsführer) with names been disclosed? (Name(n) der Geschäftsführer)</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
       <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60002</t>
+          <t>HGB-ANH-50009</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Lagebericht</t>
+          <t>Anhang</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht present the Lage (position) of the capital company so that a true and fair view (den tatsächlichen Verhältnissen entsprechendes Bild) is conveyed?</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Have the members of the supervisory board (Aufsichtsrat) been disclosed? (Mitglieder des Aufsichtsrats)</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
       <c r="G55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60003</t>
+          <t>HGB-LAG-60001</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -13589,30 +12660,26 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht contain a balanced and comprehensive analysis (ausgewogene und umfassende Analyse) appropriate to the scope and complexity of the business activities?</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht present the business progress (Geschäftsverlauf) including the business result (Geschäftsergebnis) in a manner that gives a true and fair view of the company's position?</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
       <c r="G56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60004</t>
+          <t>HGB-LAG-60003</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -13622,30 +12689,26 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht include the most significant financial performance indicators (finanzielle Leistungsindikatoren) that are material to the business activities?</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht contain a balanced and comprehensive analysis (ausgewogene und umfassende Analyse) appropriate to the scope and complexity of the business activities?</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
       <c r="G57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60005</t>
+          <t>HGB-LAG-60004</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -13655,30 +12718,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Are the financial performance indicators explained with reference to the amounts shown in the annual financial statements?</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht include the most significant financial performance indicators (finanzielle Leistungsindikatoren) that are material to the business activities?</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
       <c r="G58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60006</t>
+          <t>HGB-LAG-60005</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -13688,30 +12747,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht assess and explain the expected future development (voraussichtliche Entwicklung) including its material opportunities (Chancen) and risks (Risiken)?</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Are the financial performance indicators explained with reference to the amounts shown in the annual financial statements?</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
       <c r="G59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60007</t>
+          <t>HGB-LAG-60006</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -13721,30 +12776,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Are the underlying assumptions (Annahmen) for the expected development disclosed in the Lagebericht?</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht assess and explain the expected future development (voraussichtliche Entwicklung) including its material opportunities (Chancen) and risks (Risiken)?</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
       <c r="G60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60008</t>
+          <t>HGB-LAG-60007</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -13754,30 +12805,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht disclose the risk management objectives and methods (Risikomanagementziele und -methoden) of the company?</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Are the underlying assumptions (Annahmen) for the expected development disclosed in the Lagebericht?</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
       <c r="G61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60009</t>
+          <t>HGB-LAG-60008</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -13787,30 +12834,26 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht disclose the methods used to hedge all important types of transactions that are recognised in hedge accounting?</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht disclose the risk management objectives and methods (Risikomanagementziele und -methoden) of the company?</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
       <c r="G62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60010</t>
+          <t>HGB-LAG-60009</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -13820,30 +12863,26 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht disclose price change risks (Preisänderungsrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht disclose the methods used to hedge all important types of transactions that are recognised in hedge accounting?</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
       <c r="G63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60011</t>
+          <t>HGB-LAG-60010</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -13853,30 +12892,26 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht disclose default risks (Ausfallrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht disclose price change risks (Preisänderungsrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
       <c r="G64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60012</t>
+          <t>HGB-LAG-60011</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -13886,30 +12921,26 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht disclose liquidity risks (Liquiditätsrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht disclose default risks (Ausfallrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
       <c r="G65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60013</t>
+          <t>HGB-LAG-60012</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -13919,30 +12950,26 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht disclose risks from payment flow fluctuations (Zahlungsstromschwankungen) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht disclose liquidity risks (Liquiditätsrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
       <c r="G66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60014</t>
+          <t>HGB-LAG-60013</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -13952,30 +12979,26 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht include disclosure on the research and development area (Bereich Forschung und Entwicklung)?</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht disclose risks from payment flow fluctuations (Zahlungsstromschwankungen) to which the company is exposed, in relation to the use of financial instruments?</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
       <c r="G67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60015</t>
+          <t>HGB-LAG-60014</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -13985,30 +13008,26 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht disclose existing branch offices (bestehende Zweigniederlassungen) of the company?</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht include disclosure on the research and development area (Bereich Forschung und Entwicklung)?</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
       <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>HGB-LAG-60016</t>
+          <t>HGB-LAG-60015</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -14018,58 +13037,79 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Does the Lagebericht describe the essential features of the internal control system (wesentliche Merkmale des internen Kontrollsystems) in relation to the accounting process?</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
+          <t>Does the Lagebericht disclose existing branch offices (bestehende Zweigniederlassungen) of the company?</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
       <c r="G69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>HGB-LAG-60016</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Lagebericht</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Does the Lagebericht describe the essential features of the internal control system (wesentliche Merkmale des internen Kontrollsystems) in relation to the accounting process?</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
           <t>HGB-LAG-60017</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Lagebericht</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Does the Lagebericht describe the essential features of the risk management system (wesentliche Merkmale des Risikomanagementsystems) in relation to the accounting process?</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>PDF_EXTRACTION_LIMIT</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Item requires detailed review - not clearly determinable from PDF</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>MISSING_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/v2/output/results.xlsx
+++ b/v2/output/results.xlsx
@@ -36,7 +36,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -98,9 +92,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -542,7 +533,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
@@ -552,7 +543,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -562,7 +553,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -583,7 +574,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -641,10 +632,10 @@
         <v>62</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -654,7 +645,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -668,20 +659,20 @@
         <v>44</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -695,20 +686,20 @@
         <v>50</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -722,10 +713,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -735,7 +726,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -901,11 +892,27 @@
         </is>
       </c>
       <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Found 27 matches in PDF</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -949,21 +956,33 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Found 16 matches in PDF</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1013,11 +1032,27 @@
         </is>
       </c>
       <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Found 16 matches in PDF</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1061,21 +1096,33 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Found 25 matches in PDF</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1125,11 +1172,27 @@
         </is>
       </c>
       <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Found 15 matches in PDF</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1173,21 +1236,33 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Found 17 matches in PDF</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1237,11 +1312,27 @@
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Found 21 matches in PDF</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1291,11 +1382,27 @@
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Found 20 matches in PDF</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1345,11 +1452,27 @@
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1399,11 +1522,27 @@
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Found 14 matches in PDF</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1453,11 +1592,27 @@
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Found 14 matches in PDF</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1501,21 +1656,33 @@
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Found 16 matches in PDF</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1565,11 +1732,27 @@
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Found 20 matches in PDF</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1613,21 +1796,33 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Found 14 matches in PDF</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1677,11 +1872,27 @@
         </is>
       </c>
       <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Found 18 matches in PDF</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1725,21 +1936,33 @@
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Found 15 matches in PDF</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1789,11 +2012,27 @@
         </is>
       </c>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Found 15 matches in PDF</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1843,11 +2082,27 @@
         </is>
       </c>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Found 15 matches in PDF</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1897,11 +2152,27 @@
         </is>
       </c>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Found 18 matches in PDF</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1951,11 +2222,27 @@
         </is>
       </c>
       <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Found 22 matches in PDF</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2005,11 +2292,27 @@
         </is>
       </c>
       <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Found 22 matches in PDF</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2059,11 +2362,27 @@
         </is>
       </c>
       <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Found 22 matches in PDF</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2113,11 +2432,27 @@
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Found 22 matches in PDF</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2167,11 +2502,27 @@
         </is>
       </c>
       <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Found 22 matches in PDF</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2215,21 +2566,33 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Found 14 matches in PDF</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2279,11 +2642,27 @@
         </is>
       </c>
       <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2333,11 +2712,27 @@
         </is>
       </c>
       <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Found 25 matches in PDF</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2387,11 +2782,27 @@
         </is>
       </c>
       <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2445,11 +2856,27 @@
         </is>
       </c>
       <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2499,11 +2926,27 @@
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Found 34 matches in PDF</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2553,11 +2996,27 @@
         </is>
       </c>
       <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2607,11 +3066,27 @@
         </is>
       </c>
       <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2661,11 +3136,27 @@
         </is>
       </c>
       <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2715,11 +3206,27 @@
         </is>
       </c>
       <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2773,11 +3280,27 @@
         </is>
       </c>
       <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2825,21 +3348,33 @@
           <t>If the Articles of Association require additional reserves to be set aside</t>
         </is>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2889,11 +3424,27 @@
         </is>
       </c>
       <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2943,11 +3494,27 @@
         </is>
       </c>
       <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Found 32 matches in PDF</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2997,11 +3564,27 @@
         </is>
       </c>
       <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Found 34 matches in PDF</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3051,11 +3634,27 @@
         </is>
       </c>
       <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Found 18 matches in PDF</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3105,11 +3704,27 @@
         </is>
       </c>
       <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Found 18 matches in PDF</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3159,11 +3774,27 @@
         </is>
       </c>
       <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Found 5 matches in PDF</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3213,11 +3844,27 @@
         </is>
       </c>
       <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Found 18 matches in PDF</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3267,11 +3914,27 @@
         </is>
       </c>
       <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Found 18 matches in PDF</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3321,11 +3984,27 @@
         </is>
       </c>
       <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3375,11 +4054,27 @@
         </is>
       </c>
       <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3423,21 +4118,33 @@
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3487,11 +4194,27 @@
         </is>
       </c>
       <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3535,21 +4258,33 @@
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3599,11 +4334,27 @@
         </is>
       </c>
       <c r="K51" s="2" t="n"/>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3647,21 +4398,33 @@
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3711,11 +4474,27 @@
         </is>
       </c>
       <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr"/>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3765,11 +4544,27 @@
         </is>
       </c>
       <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr"/>
-      <c r="P54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3819,11 +4614,27 @@
         </is>
       </c>
       <c r="K55" s="2" t="n"/>
-      <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr"/>
-      <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3873,11 +4684,27 @@
         </is>
       </c>
       <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Found 21 matches in PDF</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3927,11 +4754,27 @@
         </is>
       </c>
       <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr"/>
-      <c r="O57" s="2" t="inlineStr"/>
-      <c r="P57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3981,11 +4824,27 @@
         </is>
       </c>
       <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4035,11 +4894,27 @@
         </is>
       </c>
       <c r="K59" s="2" t="n"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="2" t="inlineStr"/>
-      <c r="P59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4089,11 +4964,27 @@
         </is>
       </c>
       <c r="K60" s="2" t="n"/>
-      <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Found 2 matches in PDF</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4143,11 +5034,27 @@
         </is>
       </c>
       <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Found 25 matches in PDF</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr"/>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4191,21 +5098,33 @@
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4259,11 +5178,27 @@
         </is>
       </c>
       <c r="K63" s="2" t="n"/>
-      <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>Found 18 matches in PDF</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr"/>
-      <c r="O63" s="2" t="inlineStr"/>
-      <c r="P63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4427,11 +5362,27 @@
         </is>
       </c>
       <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Found 46 matches in PDF</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4475,21 +5426,33 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Found 24 matches in PDF</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4539,11 +5502,27 @@
         </is>
       </c>
       <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4593,11 +5572,27 @@
         </is>
       </c>
       <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4641,21 +5636,33 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -4699,21 +5706,33 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -4763,11 +5782,27 @@
         </is>
       </c>
       <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Found 25 matches in PDF</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -4817,11 +5852,27 @@
         </is>
       </c>
       <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Found 28 matches in PDF</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4871,11 +5922,27 @@
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Found 24 matches in PDF</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -4925,11 +5992,27 @@
         </is>
       </c>
       <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4979,11 +6062,27 @@
         </is>
       </c>
       <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5033,11 +6132,27 @@
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Found 29 matches in PDF</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -5087,11 +6202,27 @@
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Found 24 matches in PDF</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -5141,11 +6272,27 @@
         </is>
       </c>
       <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Found 32 matches in PDF</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -5195,11 +6342,27 @@
         </is>
       </c>
       <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Found 24 matches in PDF</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -5249,11 +6412,27 @@
         </is>
       </c>
       <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Found 25 matches in PDF</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -5303,11 +6482,27 @@
         </is>
       </c>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Found 24 matches in PDF</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -5357,11 +6552,27 @@
         </is>
       </c>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -5411,11 +6622,27 @@
         </is>
       </c>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5465,11 +6692,27 @@
         </is>
       </c>
       <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -5519,11 +6762,27 @@
         </is>
       </c>
       <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Found 26 matches in PDF</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5573,11 +6832,27 @@
         </is>
       </c>
       <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5627,11 +6902,27 @@
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5681,11 +6972,27 @@
         </is>
       </c>
       <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Found 24 matches in PDF</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5735,11 +7042,27 @@
         </is>
       </c>
       <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Found 24 matches in PDF</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5789,11 +7112,27 @@
         </is>
       </c>
       <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Found 38 matches in PDF</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5843,11 +7182,27 @@
         </is>
       </c>
       <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Found 38 matches in PDF</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5891,21 +7246,33 @@
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Found 4 matches in PDF</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5949,21 +7316,33 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6011,21 +7390,33 @@
           <t>If material changes in business activities require reclassification of prior year figures</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Found 3 matches in PDF</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6073,21 +7464,33 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Found 3 matches in PDF</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6135,21 +7538,33 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Found 3 matches in PDF</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6197,21 +7612,33 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Found 3 matches in PDF</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6259,21 +7686,33 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Found 6 matches in PDF</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6321,21 +7760,33 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Found 6 matches in PDF</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6383,21 +7834,33 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Found 3 matches in PDF</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -6445,21 +7908,33 @@
           <t>If disclosure is not prohibited by §286 Abs. 2 and would not cause significant harm to the company</t>
         </is>
       </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Found 10 matches in PDF</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -6507,21 +7982,33 @@
           <t>If disclosure is not prohibited by §286 Abs. 2 and would not cause significant harm to the company</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Found 6 matches in PDF</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -6569,21 +8056,33 @@
           <t>If disclosure per §285 Nr. 14 would seriously harm the company</t>
         </is>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Found 4 matches in PDF</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -6633,19 +8132,35 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>EXEMPTION_CLAIMED</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6693,21 +8208,33 @@
           <t>If §288 Abs. 2 applies (medium-sized GmbH)</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Found 3 matches in PDF</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -6751,21 +8278,33 @@
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6809,21 +8348,33 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -6867,21 +8418,33 @@
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Found 23 matches in PDF</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7039,21 +8602,33 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -7097,21 +8672,33 @@
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7155,21 +8742,33 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7215,19 +8814,35 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - entity does not have subsidiaries/parent/group</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -7271,21 +8886,33 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Found 2 matches in PDF</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -7331,19 +8958,35 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - entity does not have subsidiaries/parent/group</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -7391,21 +9034,33 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Found 1 matches in PDF</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -7449,21 +9104,33 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Found 2 matches in PDF</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -7507,17 +9174,37 @@
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -7563,19 +9250,35 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -7623,7 +9326,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7633,11 +9336,27 @@
           <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -7685,21 +9404,33 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Found 2 matches in PDF</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -7743,21 +9474,33 @@
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Found 5 matches in PDF</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -7801,17 +9544,37 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -7861,11 +9624,27 @@
         </is>
       </c>
       <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -7909,21 +9688,33 @@
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -7969,19 +9760,35 @@
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -8027,19 +9834,35 @@
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Protected under §286 Abs. 4 HGB</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -8085,19 +9908,35 @@
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Protected under §286 Abs. 4 HGB</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -8143,19 +9982,35 @@
       <c r="I21" s="2" t="inlineStr"/>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Protected under §286 Abs. 4 HGB</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -8203,7 +10058,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8213,11 +10068,27 @@
           <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
-      <c r="P22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -8263,19 +10134,35 @@
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - entity does not have subsidiaries/parent/group</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -8319,17 +10206,37 @@
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="inlineStr"/>
-      <c r="M24" s="2" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - entity does not have subsidiaries/parent/group</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -8375,19 +10282,35 @@
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - entity does not have subsidiaries/parent/group</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -8435,7 +10358,7 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8445,11 +10368,27 @@
           <t>EXEMPTION_CLAIMED</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
-      <c r="M26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Exempt for medium GmbH per §288 Abs. 2 HGB</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -8495,19 +10434,35 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable - entity does not have subsidiaries/parent/group</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -8553,19 +10508,35 @@
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -8615,11 +10586,27 @@
         </is>
       </c>
       <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Found 1 matches in PDF</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -8665,19 +10652,35 @@
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr"/>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -8721,17 +10724,37 @@
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="inlineStr"/>
-      <c r="M31" s="2" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -8777,19 +10800,35 @@
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -8835,19 +10874,35 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -8895,21 +10950,33 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Found 1 matches in PDF</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -8953,17 +11020,37 @@
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -9007,21 +11094,33 @@
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Found 13 matches in PDF</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -9069,21 +11168,37 @@
           <t>Exempt for medium GmbH per §288 Abs. 2 HGB - not required to disclose</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -9129,19 +11244,35 @@
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -9191,19 +11322,35 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -9247,17 +11394,37 @@
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="inlineStr"/>
-      <c r="M40" s="2" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="2" t="inlineStr"/>
-      <c r="P40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -9301,21 +11468,33 @@
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Found 4 matches in PDF</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -9365,11 +11544,27 @@
         </is>
       </c>
       <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="inlineStr"/>
-      <c r="M42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Found 17 matches in PDF</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr"/>
-      <c r="O42" s="2" t="inlineStr"/>
-      <c r="P42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -9415,19 +11610,35 @@
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr"/>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -9471,17 +11682,37 @@
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="inlineStr"/>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="2" t="inlineStr"/>
-      <c r="P44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -9527,19 +11758,35 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr"/>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9583,21 +11830,33 @@
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr"/>
-      <c r="M46" s="2" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Found 2 matches in PDF</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr"/>
-      <c r="P46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9647,11 +11906,27 @@
         </is>
       </c>
       <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="inlineStr"/>
-      <c r="M47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Found 4 matches in PDF</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9697,19 +11972,35 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9757,21 +12048,37 @@
           <t>Entity claims §288 Abs. 2 exemption</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr"/>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9819,21 +12126,37 @@
           <t>Entity claims §288 Abs. 2 exemption</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr"/>
-      <c r="O50" s="2" t="inlineStr"/>
-      <c r="P50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9881,21 +12204,37 @@
           <t>Entity invokes 5-year exemption under §288 Abs. 1</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>EXEMPTION_CLAIMED</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>ENTITY_SPECIFIC</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>No evidence found in PDF - likely not applicable or exempt</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10053,21 +12392,33 @@
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Found 20 matches in PDF</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -10117,11 +12468,27 @@
         </is>
       </c>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Found 21 matches in PDF</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -10165,21 +12532,33 @@
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -10223,21 +12602,33 @@
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -10281,21 +12672,33 @@
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -10339,21 +12742,33 @@
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Found 37 matches in PDF</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -10397,21 +12812,33 @@
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Found 21 matches in PDF</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -10455,21 +12882,33 @@
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -10517,21 +12956,33 @@
           <t>If the company uses hedge accounting (Bilanzierung von Sicherungsgeschäften)</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
-      <c r="M10" s="2" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Found 22 matches in PDF</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -10579,21 +13030,33 @@
           <t>If price change risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -10641,21 +13104,33 @@
           <t>If default risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -10703,21 +13178,33 @@
           <t>If liquidity risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -10765,21 +13252,33 @@
           <t>If cash flow fluctuation risks are material for assessing the company's position or expected development</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -10823,21 +13322,33 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -10881,21 +13392,33 @@
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -10943,21 +13466,33 @@
           <t>If the company is a capital market oriented company (§ 264d HGB - Kapitalmarktorientierte Kapitalgesellschaft)</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -11005,21 +13540,33 @@
           <t>If the company is a capital market oriented company (§ 264d HGB - Kapitalmarktorientierte Kapitalgesellschaft)</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Found 19 matches in PDF</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
-      <c r="P18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>verification-agent-v5</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11032,7 +13579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11081,2036 +13628,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-10002</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Is selbst geschaffene gewerbliche Schutzrechte (self-created industrial property rights) disclosed separately from entgeltlich erworbene (acquired) items?</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-10004</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Are geleistete Anzahlungen on intangible assets disclosed as prepayments on non-current assets?</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-10006</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Are Grundstücke und grundstücksgleiche Rechte (land and land rights) including buildings on third-party land disclosed separately?</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-10012</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Are Ausleihungen (loans) to affiliated companies and to companies with participation interests disclosed separately from equity items?</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-10014</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Are sonstige Ausleihungen (other loans) disclosed as a final line item under financial assets?</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-10021</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Are Roh-, Hilfs- und Betriebsstoffe (raw materials, consumables, and supplies) disclosed separately?</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-10030</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Are Wertpapiere (securities) classified in current assets split into shares in affiliates and other securities?</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-20007</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Are satzungsmäßige Rücklagen (statutory reserves per articles of association) disclosed separately?</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-20021</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Are Anleihen (bonds) disclosed, with a sub-row showing the convertible portion if applicable?</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-20023</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Are erhaltene Anzahlungen auf Bestellungen (advance payments received on orders) disclosed separately?</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-20025</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Are liabilities from accepted drafts (Wechselverbindlichkeiten) disclosed separately?</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>HGB-BIL-20035</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Bilanz</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Is the total amount of liabilities secured by collateral (Pfandbriefe, etc.) disclosed per §285 No. 3a?</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30002</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Revenue (Umsatzerlöse) - Line item 1 of Gesamtkostenverfahren</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30005</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Total operating performance (Gesamtleistung) - Calculated from lines 1-3</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30006</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Cost of materials (Materialaufwand) - Line item 4</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30030</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Does the entity have a chart of accounts (Kontenplan) that maps to the Gesamtkostenverfahren line items per §275 Abs. 2 HGB?</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30031</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Are comparative figures for the prior financial year disclosed in the GuV per §275 Abs. 3 HGB?</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30032</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Are items in the GuV presented in accordance with the prior year's classification if any material changes in business activities require reclassification per §275 Abs. 4 HGB?</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30060</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Is revenue broken down by business activity (Tätigkeit) per §285 Nr. 14 HGB?</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30061</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Is revenue broken down by geographic market ( Märkte) per §285 Nr. 14 HGB?</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30070</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>If revenue breakdown by activity or geography is not disclosed, has the entity invoked the protective clause under §286 Abs. 2 HGB?</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30080</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Is the entity eligible for exemptions under §288 Abs. 2 HGB for medium-sized GmbH?</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30082</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Is the entity required to provide a management report (Lagebericht) despite being medium-sized under §289 HGB?</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30090</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Is there a clear presentation of the GuV using the vertically aligned format per §275 Abs. 1 HGB?</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>HGB-GUV-30091</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>GuV</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Are material items in the GuV not netted but shown separately per §265 Abs. 7 HGB?</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40001</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Have the accounting and valuation methods used been disclosed? (Bilanzierungsmethoden)</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40002</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Have any changes to accounting and valuation methods been disclosed with justification? (Änderung der Bilanzierungsmethoden)</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40003</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Has the impact of any material changes in estimates been disclosed? (Wesentliche Schätzungsänderungen)</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40101</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Has the name and registered office of subsidiaries been disclosed? (Name und Sitz von Tochterunternehmen)</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40102</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Has the equity ( Eigenkapital) of subsidiaries been disclosed? (Eigenkapital der Tochterunternehmen)</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40103</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Has an exemption from preparing consolidated accounts (Konzernabschluss) been disclosed with reasons and criteria? (Befreiung von Konzernabschluss)</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40105</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Has a disclosure of stock movements / changes in inventories been made? (Vorratsbestandsveränderung)</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40107</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Has research and development (Forschung und Entwicklung) expenditure been disclosed? (Forschungs- und Entwicklungskosten)</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40110</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Have depreciation and amortization methods and periods been disclosed? (Abschreibungsmethoden)</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40113</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Have any restatements of prior year figures (Rückwirkung von Bilanzänderungen) been disclosed? (Rückwirkende Änderungen)</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40114</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Have subsequent events (nachträgliche Ereignisse) after the balance sheet date been disclosed? (Nachtragsbericht)</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40115</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Has the average number of employees (Durchschnittszahl der Beschäftigten) been disclosed? (Beschäftigtenzahl)</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40115</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Have audit fees (Honorar des Abschlussprüfers) for the auditor been disclosed? (Abschlussprüferhonorar)</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40116</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Has management remuneration (Vorstands-/Geschäftsführungsvergütung) been disclosed individually or in aggregate? (Gesamtbezüge der Organmitglieder)</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40118</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Has any share-based payment (aktienbasierte Vergütung) been disclosed? (Aktienbasierte Vergütung)</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40120</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Has parent company information (Mutterunternehmen) been disclosed? (Mutterunternehmen)</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40122</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Has information on consolidated entities (Konsolidierungskreis) been disclosed? (Tochterunternehmen im Konzernabschluss)</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40123</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Has information on branch offices (Zweigniederlassungen) been disclosed? (Zweigniederlassungen)</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40125</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Have audit fees been broken down by activity (Abschlussprüferleistungen)? (Aufschlüsselung des Prüfungshonorars)</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40127</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Has a statement on the use of the exemption under §264 Abs. 3 HGB (small company relief) been made? (Handelsrechtliche Befreiung)</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40128</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Has the disclosure of financial instruments at fair value (Bewertungseinheiten) been made? (Bewertungseinheiten)</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40131</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Has a statement on the recognition and measurement of lease assets and liabilities been disclosed? (Leasingangaben)</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40133</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Has a statement on the underlying currency for significant transactions been disclosed? (Währungsangaben)</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-40201</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Has the protective clause (Schutzklausel) under §286 HGB been invoked appropriately? (Befreiung von Einzelangaben)</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-50002</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Has a statement on the assumption of going concern (Fortführung der Unternehmenstätigkeit) been disclosed? (Going-Concern-Annahme)</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-50004</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Has the legal form (Rechtsform) of the entity been disclosed? (Rechtsform)</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-50006</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Has the company's object (Unternehmensgegenstand) been disclosed? (Gegenstand des Unternehmens)</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-50007</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Has a list of managing directors (Geschäftsführer) with names been disclosed? (Name(n) der Geschäftsführer)</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>HGB-ANH-50009</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Anhang</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Have the members of the supervisory board (Aufsichtsrat) been disclosed? (Mitglieder des Aufsichtsrats)</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60001</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht present the business progress (Geschäftsverlauf) including the business result (Geschäftsergebnis) in a manner that gives a true and fair view of the company's position?</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60003</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht contain a balanced and comprehensive analysis (ausgewogene und umfassende Analyse) appropriate to the scope and complexity of the business activities?</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60004</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht include the most significant financial performance indicators (finanzielle Leistungsindikatoren) that are material to the business activities?</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60005</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Are the financial performance indicators explained with reference to the amounts shown in the annual financial statements?</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60006</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht assess and explain the expected future development (voraussichtliche Entwicklung) including its material opportunities (Chancen) and risks (Risiken)?</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60007</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Are the underlying assumptions (Annahmen) for the expected development disclosed in the Lagebericht?</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60008</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose the risk management objectives and methods (Risikomanagementziele und -methoden) of the company?</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60009</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose the methods used to hedge all important types of transactions that are recognised in hedge accounting?</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60010</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose price change risks (Preisänderungsrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60011</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose default risks (Ausfallrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60012</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose liquidity risks (Liquiditätsrisiken) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60013</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose risks from payment flow fluctuations (Zahlungsstromschwankungen) to which the company is exposed, in relation to the use of financial instruments?</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60014</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht include disclosure on the research and development area (Bereich Forschung und Entwicklung)?</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60015</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht disclose existing branch offices (bestehende Zweigniederlassungen) of the company?</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60016</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht describe the essential features of the internal control system (wesentliche Merkmale des internen Kontrollsystems) in relation to the accounting process?</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>HGB-LAG-60017</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Lagebericht</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Does the Lagebericht describe the essential features of the risk management system (wesentliche Merkmale des Risikomanagementsystems) in relation to the accounting process?</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>MISSING_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/v2/output/results.xlsx
+++ b/v2/output/results.xlsx
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -686,13 +686,13 @@
         <v>50</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -9174,24 +9174,20 @@
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>ENTITY_SPECIFIC</t>
-        </is>
-      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Found in PDF text</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
@@ -9248,24 +9244,20 @@
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>ENTITY_SPECIFIC</t>
-        </is>
-      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Found in PDF text</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
@@ -9544,24 +9536,20 @@
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>ENTITY_SPECIFIC</t>
-        </is>
-      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Found in PDF text</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr"/>
@@ -9758,24 +9746,20 @@
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>ENTITY_SPECIFIC</t>
-        </is>
-      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Found in PDF text</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
@@ -10650,24 +10634,20 @@
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>ENTITY_SPECIFIC</t>
-        </is>
-      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Found in PDF text</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
@@ -10736,12 +10716,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Not applicable to this entity</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
@@ -10884,12 +10864,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Not applicable to this entity</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr"/>
@@ -11032,12 +11012,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Not applicable to this entity</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr"/>
@@ -11180,12 +11160,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Not applicable to this entity</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
@@ -11254,12 +11234,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Not applicable to this entity</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr"/>
@@ -11320,24 +11300,20 @@
           <t>Entity claims §286 exemption for specific disclosures</t>
         </is>
       </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>ENTITY_SPECIFIC</t>
-        </is>
-      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>No evidence found in PDF - likely not applicable or exempt</t>
+          <t>Found in PDF text</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr"/>
